--- a/Excel/12_SupplementaryCO2_WIP_v02.xlsx
+++ b/Excel/12_SupplementaryCO2_WIP_v02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D605146-D02A-4D87-9072-BC536C62C466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9B026F-A196-4BCC-AC40-FAEF48545636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="0" windowWidth="34605" windowHeight="18645" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -1803,73 +1803,16 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1" tint="0.249977111117893"/>
+        <sz val="11"/>
+        <color theme="1"/>
         <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1" tint="0.14999847407452621"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0" tint="-5.0965910824915313E-2"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2724,16 +2667,73 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color theme="1" tint="0.249977111117893"/>
         <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1" tint="0.14999847407452621"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0" tint="-5.0965910824915313E-2"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3837,14 +3837,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6E44059A-C219-4316-A7A0-AD77B0121F06}" name="Table_Input_SupplementaryCO2" displayName="Table_Input_SupplementaryCO2" ref="D9:E11" totalsRowDxfId="13" headerRowCellStyle="Input table column header">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6E44059A-C219-4316-A7A0-AD77B0121F06}" name="Table_Input_SupplementaryCO2" displayName="Table_Input_SupplementaryCO2" ref="D9:E11" totalsRowDxfId="49" headerRowCellStyle="Input table column header">
   <autoFilter ref="D9:E11" xr:uid="{6E44059A-C219-4316-A7A0-AD77B0121F06}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="2" xr3:uid="{9540E705-999C-466B-A6B4-24C60E9153AE}" name="Usage description" totalsRowFunction="average" totalsRowDxfId="12" dataCellStyle="Input text" totalsRowCellStyle="Input select"/>
-    <tableColumn id="4" xr3:uid="{9DFFE0DC-C289-47FB-8F0C-2D2F480EEE4C}" name="Amount used (kg)" totalsRowDxfId="11" totalsRowCellStyle="Content bold"/>
+    <tableColumn id="2" xr3:uid="{9540E705-999C-466B-A6B4-24C60E9153AE}" name="Usage description" totalsRowFunction="average" totalsRowDxfId="48" dataCellStyle="Input text" totalsRowCellStyle="Input select"/>
+    <tableColumn id="4" xr3:uid="{9DFFE0DC-C289-47FB-8F0C-2D2F480EEE4C}" name="Amount used (kg)" totalsRowDxfId="47" totalsRowCellStyle="Content bold"/>
   </tableColumns>
   <tableStyleInfo name="Editable table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3896,7 +3896,7 @@
     <tableColumn id="1" xr3:uid="{94E6DCBF-2F6C-4DEA-850E-1257E85423A4}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C9F029D9-51B8-4816-85D5-3441B1755CA7}" name="FracWET" dataDxfId="33">
+    <tableColumn id="2" xr3:uid="{C9F029D9-51B8-4816-85D5-3441B1755CA7}" name="FracWET" dataDxfId="30">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3944,7 +3944,7 @@
     <tableColumn id="1" xr3:uid="{814E6C27-AEC4-4F58-94DF-EB6BF6F8DEE2}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B95AAA77-7FB1-4F2D-8530-6B063DBAAC65}" name="FracWET" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{B95AAA77-7FB1-4F2D-8530-6B063DBAAC65}" name="FracWET" dataDxfId="29" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3962,7 +3962,7 @@
     <tableColumn id="1" xr3:uid="{22812ECF-2BDF-479B-BDD0-ABDD9D181FA2}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F6379345-454B-47D5-B6BF-10AC3FD1C963}" name="EFPRP" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F6379345-454B-47D5-B6BF-10AC3FD1C963}" name="EFPRP" dataDxfId="28" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3980,7 +3980,7 @@
     <tableColumn id="1" xr3:uid="{39B089BF-12E1-4543-87BC-10C6A0C6FFD9}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1F8FDC7C-6656-4185-B6E7-8E523E08EB97}" name="Season" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1F8FDC7C-6656-4185-B6E7-8E523E08EB97}" name="Season" dataDxfId="27" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4012,49 +4012,49 @@
     <tableColumn id="1" xr3:uid="{6ADC392C-5850-4DF1-B61E-AD89C6F0C73A}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{BB6F7FCE-22AE-4D28-A913-77E6DA4EEDBA}" name="MAT (ºC)" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{BB6F7FCE-22AE-4D28-A913-77E6DA4EEDBA}" name="MAT (ºC)" dataDxfId="26" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{13CC30B5-CFBC-4FBD-A997-7404CA96F1DC}" name="Anaerobic lagoon" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{13CC30B5-CFBC-4FBD-A997-7404CA96F1DC}" name="Anaerobic lagoon" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8377B2BA-D9A3-4F3B-9CDA-463B9C7C6D0B}" name="Digester / covered lagoons" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{8377B2BA-D9A3-4F3B-9CDA-463B9C7C6D0B}" name="Digester / covered lagoons" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8F8FE17C-A26D-4015-8DE7-8A0284CCF305}" name="Liquid systems" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{8F8FE17C-A26D-4015-8DE7-8A0284CCF305}" name="Liquid systems" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{335544B6-26CF-4063-8B41-14ACFA814834}" name="Daily spread" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{335544B6-26CF-4063-8B41-14ACFA814834}" name="Daily spread" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{ED337F61-FBEF-437D-B2EA-429DF88BF98B}" name="Composting (passive windrow)" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{ED337F61-FBEF-437D-B2EA-429DF88BF98B}" name="Composting (passive windrow)" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7A316A78-DAB2-4C8A-BD7A-5BAB30008B7C}" name="Solid storage" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{7A316A78-DAB2-4C8A-BD7A-5BAB30008B7C}" name="Solid storage" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{ED235F5C-8782-4085-ACE9-5581BEFF0447}" name="Pit storage" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{ED235F5C-8782-4085-ACE9-5581BEFF0447}" name="Pit storage" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{82BDA5BE-621D-463B-8C21-FE2122E0D19D}" name="Deep litter" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{82BDA5BE-621D-463B-8C21-FE2122E0D19D}" name="Deep litter" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{A89BA2F9-19A1-47F2-B204-07445F32B7EA}" name="Poultry manure with bedding" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{A89BA2F9-19A1-47F2-B204-07445F32B7EA}" name="Poultry manure with bedding" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{5843EC54-CAD6-4A10-8170-CA7C4C5ED5F5}" name="Poultry manure without bedding" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{5843EC54-CAD6-4A10-8170-CA7C4C5ED5F5}" name="Poultry manure without bedding" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{8DE32C71-B502-409B-928F-750CCA16648F}" name="Direct processing" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{8DE32C71-B502-409B-928F-750CCA16648F}" name="Direct processing" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{27CA3685-3894-4D69-B24B-CA075337B41C}" name="Direct application" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{27CA3685-3894-4D69-B24B-CA075337B41C}" name="Direct application" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{99559C44-EEE8-4D8F-A9A8-FCC203F32BB3}" name="Pasture range and paddock" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{99559C44-EEE8-4D8F-A9A8-FCC203F32BB3}" name="Pasture range and paddock" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{66B87B0B-81DA-4A7A-9AF4-43E1B0D7455E}" name="MAT raw" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{66B87B0B-81DA-4A7A-9AF4-43E1B0D7455E}" name="MAT raw" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4072,7 +4072,7 @@
     <tableColumn id="1" xr3:uid="{DB5A1BF0-2654-4654-A005-25B68250353F}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DC92C861-4FEA-4BB5-A89C-E12CFC7C9D9E}" name="EFNi &amp; EFN2Oi" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{DC92C861-4FEA-4BB5-A89C-E12CFC7C9D9E}" name="EFNi &amp; EFN2Oi" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4188,49 +4188,49 @@
     <tableColumn id="1" xr3:uid="{8D40750F-7330-456A-BB21-E3EFB286833F}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{62E66C4A-4479-4A17-B98A-2F53B0DF4466}" name="MAT" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{62E66C4A-4479-4A17-B98A-2F53B0DF4466}" name="MAT" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B9FC8F4B-35F5-4F7B-8E1C-CE583C7FC041}" name="MAP" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{B9FC8F4B-35F5-4F7B-8E1C-CE583C7FC041}" name="MAP" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{380F7CFF-6056-41A6-BF80-BBCCEE00662F}" name="Frost days per year" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{380F7CFF-6056-41A6-BF80-BBCCEE00662F}" name="Frost days per year" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{02CC8E12-B022-4DEC-B7E6-726532DF5644}" name="Elevation" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{02CC8E12-B022-4DEC-B7E6-726532DF5644}" name="Elevation" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{115D7C7A-B275-48F4-8B1D-23731CD5E9FD}" name="MAP:PET" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{115D7C7A-B275-48F4-8B1D-23731CD5E9FD}" name="MAP:PET" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{4116C12D-F410-4E10-93F9-6434C598BA9E}" name="Min temp" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{4116C12D-F410-4E10-93F9-6434C598BA9E}" name="Min temp" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{540A3023-64D8-4CEB-8D95-A6D179AA549E}" name="Max temp" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{540A3023-64D8-4CEB-8D95-A6D179AA549E}" name="Max temp" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{D64547E2-0462-4E06-854A-CCF17A6318D7}" name="Min rainfall" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{D64547E2-0462-4E06-854A-CCF17A6318D7}" name="Min rainfall" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{655EDD60-857F-42AC-A2BF-DEC3DFB090B0}" name="Max rainfall" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{655EDD60-857F-42AC-A2BF-DEC3DFB090B0}" name="Max rainfall" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{7278EB04-7DA4-4E3B-919C-4FEB67D4C659}" name="Min frost days" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{7278EB04-7DA4-4E3B-919C-4FEB67D4C659}" name="Min frost days" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{BE43C499-B1F6-40CB-823D-961D21AEEAA3}" name="Max frost days" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{BE43C499-B1F6-40CB-823D-961D21AEEAA3}" name="Max frost days" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{D03997E9-53F2-4697-B878-CFFFC9520B10}" name="Min elevation" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{D03997E9-53F2-4697-B878-CFFFC9520B10}" name="Min elevation" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{C44A8FA0-40DC-4D7B-94F7-F219584A1AD7}" name="Max elevation" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{C44A8FA0-40DC-4D7B-94F7-F219584A1AD7}" name="Max elevation" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{A2246660-C845-4D9C-9366-7ECECC01DF7C}" name="Min MAP:PET" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{A2246660-C845-4D9C-9366-7ECECC01DF7C}" name="Min MAP:PET" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{AB61D1E6-3618-40D8-826C-ABEBBE7DF2B0}" name="Max MAP:PET" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{AB61D1E6-3618-40D8-826C-ABEBBE7DF2B0}" name="Max MAP:PET" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4248,7 +4248,7 @@
     <tableColumn id="1" xr3:uid="{30DD4BB3-ABE2-4C86-A881-C32DBDC5DA0E}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D6850548-4D06-4192-95CD-9B52C1BD5D14}" name="Wet or Dry Zone" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{D6850548-4D06-4192-95CD-9B52C1BD5D14}" name="Wet or Dry Zone" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4892,7 +4892,7 @@
         <v>88</v>
       </c>
       <c r="E9" s="55">
-        <f>'12.1.1-2 Supplementary CO2'!E15</f>
+        <f>VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2_Result_Method1</f>
         <v>0.2</v>
       </c>
       <c r="F9" s="55">
@@ -10430,6 +10430,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADIALgAxADoAIABTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMgAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AUQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AUQAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAIAB1AHMAZQBkACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAAoAGsAZwAgAEMATwAyACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEALABcAG4AIAAgACAAIABRACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADIALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBRAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAIAB1AHMAZQBkACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVABpAHQAbABlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBVAG4AaQB0ACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFMAbwB1AHIAYwBlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -10624,19 +10637,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADIALgAxADoAIABTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMgAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AUQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AUQAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAIAB1AHMAZQBkACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAAoAGsAZwAgAEMATwAyACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEALABcAG4AIAAgACAAIABRACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADIALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBRAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAIAB1AHMAZQBkACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVABpAHQAbABlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBVAG4AaQB0ACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFMAbwB1AHIAYwBlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -10649,6 +10649,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10667,22 +10683,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>

--- a/Excel/12_SupplementaryCO2_WIP_v02.xlsx
+++ b/Excel/12_SupplementaryCO2_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9B026F-A196-4BCC-AC40-FAEF48545636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6567C3-9735-47D0-9F71-9743D169A987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -176,6 +176,7 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Fertiliser type f","FracGASFf","Basis";"Urea-based fertilisers",0.15,"Urea";"Ammonium-based fertilisers",0.08,"Ammonium";"Nitrate-based fertilisers",0.01,"Nitrate";"Ammonium-nitrate based fertilisers",0.05,"Ammonium-nitrate";"Other fertilisers",0.11,"Other"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_NIRReference">_xlfn.LAMBDA("IPCC 2019 Refinement Volume 4 Table 11.3 [1, p. 11]")</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Source">_xlfn.LAMBDA("VEERG 2026:Table 12.2.2.9")</definedName>
@@ -10430,19 +10431,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADIALgAxADoAIABTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMgAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AUQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AUQAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAIAB1AHMAZQBkACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAAoAGsAZwAgAEMATwAyACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEALABcAG4AIAAgACAAIABRACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADIALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBRAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAIAB1AHMAZQBkACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVABpAHQAbABlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBVAG4AaQB0ACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFMAbwB1AHIAYwBlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -10637,34 +10636,31 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADIALgAxADoAIABTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMgAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AUQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AUQAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAIAB1AHMAZQBkACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAAoAGsAZwAgAEMATwAyACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEALABcAG4AIAAgACAAIABRACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADIALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBRAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAIAB1AHMAZQBkACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVABpAHQAbABlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBVAG4AaQB0ACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFMAbwB1AHIAYwBlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10683,13 +10679,18 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/12_SupplementaryCO2_WIP_v02.xlsx
+++ b/Excel/12_SupplementaryCO2_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6567C3-9735-47D0-9F71-9743D169A987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C137AC-7454-4E17-BE1C-4BC892D88E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15345" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -18,8 +18,11 @@
     <sheet name="Results" sheetId="13" r:id="rId3"/>
     <sheet name="Input - CO2 Use" sheetId="70" r:id="rId4"/>
     <sheet name="12.1.1-2 Supplementary CO2" sheetId="69" r:id="rId5"/>
-    <sheet name="Constants - Common" sheetId="122" r:id="rId6"/>
+    <sheet name="Constants - Common" sheetId="123" r:id="rId6"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId7"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -1685,116 +1688,6 @@
   <dxfs count="62">
     <dxf>
       <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -2654,6 +2547,116 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3773,6 +3776,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -3852,16 +3875,16 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{DC28F2C4-8AF6-4785-8C6B-CEC2944CC2FD}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E54D8255-E094-4664-9B87-44EA918A7397}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{294900B6-3C87-45A7-8EDB-09A3701C2F93}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{5A8FDCE2-4C01-4CF4-BC13-5E791E7C1B87}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A05DBB6D-CE50-4268-9475-32BE9CA69194}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{95C76E72-5256-4725-9123-CF12C4C2C13A}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3870,16 +3893,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{13B68031-FE71-4BE0-8C8E-1D599536502B}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{7513BCC0-3CAF-47DF-9CC1-D10B010D3C28}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{0FC876BB-4FDA-45B1-B871-317669F4973F}" name="Data source">
+    <tableColumn id="1" xr3:uid="{202B53AD-15AF-47DD-A8DF-8A644E1E62C2}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E64587BC-B612-4C18-AC5F-429A1FF42626}" name="Data score">
+    <tableColumn id="2" xr3:uid="{56455D86-FDA2-4D21-AC90-AAB3B6C4A12A}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3888,16 +3911,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{54A617B9-FF3E-410C-96A5-4B66BB130A02}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{1DA84CC2-969F-41AE-9031-F99AD7852ABE}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{94E6DCBF-2F6C-4DEA-850E-1257E85423A4}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{00A4B6C2-5609-43F5-98E4-4C50DC98E37A}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C9F029D9-51B8-4816-85D5-3441B1755CA7}" name="FracWET" dataDxfId="30">
+    <tableColumn id="2" xr3:uid="{536575A5-4C36-45FD-B79B-7400C0B9097C}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3906,7 +3929,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{448ECC07-43ED-47BD-8BF7-B67C65717D36}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{D662381A-BA07-49B3-98AC-156A7BC6DB24}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3915,19 +3938,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BB4FDCC6-81B1-46EB-A1CB-1E21FDEA30A7}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{9C35C0F7-9728-46BB-B8F2-861D1557228C}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CC0A441B-D022-4CA6-8354-A69834BFBFD8}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{AF2525F5-AE3A-4F30-A43F-DAEC57F9BBBE}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{40564AE7-BB66-48AF-B3BC-88D951DDE7ED}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{2D59F631-206A-4B3A-925D-F801963D169B}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3A8B2D33-5F9F-460C-93FA-C0088B196858}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{29AA31B1-70D1-4F51-9B50-B0765353B3A1}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{43884D9C-CB71-47BA-ADBF-C46278659C69}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{5A43BDFF-85B3-4F71-847E-5291DB5FB039}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3936,16 +3959,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{4D75122A-64DD-44AC-906A-4556B88FCA94}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{DB17A14E-10C5-4ECB-8834-F42DCFB7B612}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{814E6C27-AEC4-4F58-94DF-EB6BF6F8DEE2}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{2431C1A1-DA37-4C90-989F-1D7ECC95BC95}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B95AAA77-7FB1-4F2D-8530-6B063DBAAC65}" name="FracWET" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{32AD751C-A971-4F05-A222-D3ECFF8DEC07}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3954,16 +3977,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{A48CC38B-BA4A-461A-8A4A-F73E8E890799}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{20205C5F-34FE-4762-B6E7-EDB665BAFEAB}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{22812ECF-2BDF-479B-BDD0-ABDD9D181FA2}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{4BA23BF7-05DB-42D9-8B63-E3D6685CB1B2}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F6379345-454B-47D5-B6BF-10AC3FD1C963}" name="EFPRP" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{40309036-E4B2-49D7-8237-CF8693A73A8D}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3972,16 +3995,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{2013A3BB-DB3F-4651-BAF5-B2BC62FF8643}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{44A964C5-1B1A-4810-B29D-22E4827F6D80}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{39B089BF-12E1-4543-87BC-10C6A0C6FFD9}" name="Month">
+    <tableColumn id="1" xr3:uid="{B326F2AA-58A8-4340-A737-DF7E207ADBB9}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1F8FDC7C-6656-4185-B6E7-8E523E08EB97}" name="Season" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A280D67F-3590-45D9-B7A7-DE06E7FC2CFC}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3990,7 +4013,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{CB579B7F-3F35-4411-A973-C63A8EB50780}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{94EFE41F-3966-48A0-AFCE-F4C9333145A1}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4010,52 +4033,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{6ADC392C-5850-4DF1-B61E-AD89C6F0C73A}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{0D3EBB1F-CBE3-4F48-943E-A8E5C14B79CE}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{BB6F7FCE-22AE-4D28-A913-77E6DA4EEDBA}" name="MAT (ºC)" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3FD734E5-1A08-4F61-857C-89CB6A6BB7A4}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{13CC30B5-CFBC-4FBD-A997-7404CA96F1DC}" name="Anaerobic lagoon" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{B7E0A5A6-C943-41C8-9125-B0FD838AEEBB}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8377B2BA-D9A3-4F3B-9CDA-463B9C7C6D0B}" name="Digester / covered lagoons" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{9A9E2F12-4BC6-4014-8C09-0DC978B3D396}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8F8FE17C-A26D-4015-8DE7-8A0284CCF305}" name="Liquid systems" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{43A86789-1D5D-4506-99E5-2CE946C9B935}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{335544B6-26CF-4063-8B41-14ACFA814834}" name="Daily spread" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{FD6BD9E3-A536-4B32-BE04-8B2AA7D476FA}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{ED337F61-FBEF-437D-B2EA-429DF88BF98B}" name="Composting (passive windrow)" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{08C13AA3-9ACE-4C3B-83E8-ED0D90040928}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7A316A78-DAB2-4C8A-BD7A-5BAB30008B7C}" name="Solid storage" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{9D0A8979-2395-4107-AABD-6CF2A17A937E}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{ED235F5C-8782-4085-ACE9-5581BEFF0447}" name="Pit storage" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{77E2A6E4-4BFA-48D2-8683-A4E6221F80CC}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{82BDA5BE-621D-463B-8C21-FE2122E0D19D}" name="Deep litter" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{3459A797-CF4F-4395-9C5A-5F7D164C0BB9}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{A89BA2F9-19A1-47F2-B204-07445F32B7EA}" name="Poultry manure with bedding" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{43506916-F6F4-42BB-B3D2-F163A8758B3F}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{5843EC54-CAD6-4A10-8170-CA7C4C5ED5F5}" name="Poultry manure without bedding" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{09C53F63-61EA-431E-9466-AA55D1C98A41}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{8DE32C71-B502-409B-928F-750CCA16648F}" name="Direct processing" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{3C68D010-20B5-4E85-AFD0-B6F35C274C96}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{27CA3685-3894-4D69-B24B-CA075337B41C}" name="Direct application" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{DF09420B-372D-4044-9824-6784C359E4FB}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{99559C44-EEE8-4D8F-A9A8-FCC203F32BB3}" name="Pasture range and paddock" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{DD96BAF6-C820-4901-8631-684201BD37F1}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{66B87B0B-81DA-4A7A-9AF4-43E1B0D7455E}" name="MAT raw" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{A9667774-9497-4E14-AD0B-1966CC5C78DB}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4064,16 +4087,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{0E617B26-18D0-4AFA-82FE-00AED0900410}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{47B9CC42-DAC1-4C7A-B36D-FFEEA3D02243}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DB5A1BF0-2654-4654-A005-25B68250353F}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{EF4B9763-3A90-4CCB-BB06-7CB33C375183}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DC92C861-4FEA-4BB5-A89C-E12CFC7C9D9E}" name="EFNi &amp; EFN2Oi" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{C86A6947-CC3E-449E-88B5-D3B85478E5FE}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4082,20 +4105,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BFEFA86D-B928-4343-A1C3-8AACEDBA85DF}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DC9D5988-D4EF-4FA9-AD2F-7CE6809EDFC1}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8DC65857-1762-4DED-831A-06826FC8E599}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{A2551037-9F3E-40CA-8905-613EBF20DB28}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{FE185B29-9557-4581-BF86-603C43AB533D}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{B7FFF453-85E6-452D-997C-0C2509DCDDE3}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2A95011F-50D1-4289-9E7F-3DF967FE98BA}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{99E7FA75-0DC9-4A64-8F09-67032DD4B825}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4104,12 +4127,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4A19D36B-5E63-4974-A793-136379A355A9}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD482C2-2113-4569-A706-00AE921ED937}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{9C5723D8-D0B4-4125-9BBC-4DDD424173F8}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{91A099A5-C097-4F07-A2C8-950B961AA2B7}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4118,16 +4141,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{94DE9EAB-5015-4060-9BC2-2CD8F0DDFF50}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3DF16CDD-F8A2-45EC-8A81-7CD614F61621}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4001CBA9-F4A3-4C7D-A275-B1BA3E362739}" name="Gas">
+    <tableColumn id="1" xr3:uid="{ED2625C0-E185-4A0A-935E-8967B5B41084}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3AD90266-42FF-4CC8-A75A-9C805610DB6E}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{F358AFC6-BF6F-45EE-A0E5-FBE2D5E18CC6}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4136,7 +4159,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{C444C88D-010B-4CAA-8EC7-6D34E52C3F4A}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C8E09135-8E20-48BF-B9F9-C4C2095F7DC4}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4145,19 +4168,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3A8C0CFA-3DE9-498C-966D-6B244E120A7E}" name="Gas">
+    <tableColumn id="1" xr3:uid="{4FE22ACC-4AAE-4C9B-B5EC-31F585D9F514}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{92DAC899-6F8B-4D13-8C45-81CFF6F286F1}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{0B973D01-51E4-42EA-A52A-7B370A9818FC}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{28F8688B-CF96-482A-8C40-083526955682}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{1F60FF1E-475F-4C25-9951-5CE5CBEF269B}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8770A909-8C13-47E9-AD96-8C67877643DF}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{8A7A8DC6-1820-4468-98B3-8DC8D298768B}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D670556D-4DF6-4786-BA8A-09C654C17DB9}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{AB15569A-614B-4A65-B948-7F3332198BB8}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4166,7 +4189,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{781EDDAF-7F9B-48B0-A342-31E9122F53DD}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{32C3ED2B-152D-48F1-BD54-D2E7DC0CEC3A}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4186,52 +4209,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{8D40750F-7330-456A-BB21-E3EFB286833F}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{29BADEE5-11FA-482B-8555-5701BD405E33}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{62E66C4A-4479-4A17-B98A-2F53B0DF4466}" name="MAT" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{7B9180E5-E72F-41EB-8639-876A4B66BD50}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B9FC8F4B-35F5-4F7B-8E1C-CE583C7FC041}" name="MAP" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{FB64BEF6-3E4E-41A2-B49B-B6B5039D2DAF}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{380F7CFF-6056-41A6-BF80-BBCCEE00662F}" name="Frost days per year" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{78FC67DC-FA57-436B-9821-A52723702DA2}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{02CC8E12-B022-4DEC-B7E6-726532DF5644}" name="Elevation" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{2E77B52E-83BC-4C1B-8C1D-472000219827}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{115D7C7A-B275-48F4-8B1D-23731CD5E9FD}" name="MAP:PET" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{682EB6DE-3ADC-483A-8C67-11B2C9AD83CF}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{4116C12D-F410-4E10-93F9-6434C598BA9E}" name="Min temp" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{90C582E0-AD24-4ED3-9051-0AF1809B4DB6}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{540A3023-64D8-4CEB-8D95-A6D179AA549E}" name="Max temp" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{899D33BD-3A3E-48DB-9B14-F8F785E5EC56}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{D64547E2-0462-4E06-854A-CCF17A6318D7}" name="Min rainfall" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{D8493FFC-C1C4-428A-AF00-32143804CCAE}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{655EDD60-857F-42AC-A2BF-DEC3DFB090B0}" name="Max rainfall" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{BB2B90DB-7CFB-481C-9BB1-9F0983BCF825}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{7278EB04-7DA4-4E3B-919C-4FEB67D4C659}" name="Min frost days" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{FF6EC65F-302D-4D95-97C2-143526B36E50}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{BE43C499-B1F6-40CB-823D-961D21AEEAA3}" name="Max frost days" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{BD8B3749-226C-46EC-9FAC-9DFD01016A66}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{D03997E9-53F2-4697-B878-CFFFC9520B10}" name="Min elevation" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{5CA7B685-E4FF-415B-A071-D0565D4A0EC8}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{C44A8FA0-40DC-4D7B-94F7-F219584A1AD7}" name="Max elevation" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{703E4251-9F9A-4B5A-BDA7-EAFE87B2C251}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{A2246660-C845-4D9C-9366-7ECECC01DF7C}" name="Min MAP:PET" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{4299A7B8-62B9-439D-BE3B-86DDAC9BA7B1}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{AB61D1E6-3618-40D8-826C-ABEBBE7DF2B0}" name="Max MAP:PET" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{C7475492-A172-45FC-9D9B-8A2620899F29}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4240,16 +4263,16 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{57EBC0E9-F0EE-409B-B02B-65F95E0DBD10}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{95D2B30B-FDE4-4FCB-83C5-CC122F14B9EE}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{30DD4BB3-ABE2-4C86-A881-C32DBDC5DA0E}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{BDBE3A82-F5AB-4601-A9EC-1B58C33B4F9E}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D6850548-4D06-4192-95CD-9B52C1BD5D14}" name="Wet or Dry Zone" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{638CECC6-89F0-48CD-A20C-DEC3B9BF96DB}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4258,7 +4281,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{4DCD1AF7-0F5B-4776-A34C-5F60347B0D68}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{378BFE60-DACD-4546-9B8C-953262FD5EC6}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4266,16 +4289,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{AA691C71-D51E-4A4F-8321-B70D5A2166C7}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{3561C04F-8337-466E-8CF1-60DEFADEC820}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5E81B5F6-3184-4C46-B272-8A55D7855886}" name="MAT">
+    <tableColumn id="2" xr3:uid="{0DE9DF78-83AF-4C11-8570-5EFA5B2B38AA}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B59D4E84-94D9-4E61-A29D-6B62F741B5BA}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{BD531263-84ED-4EF0-853E-FA6AAFCE4568}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BBD14DC8-B942-4A1D-9E63-811222BB9D53}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{14E0F267-CF46-4C14-80CD-850A36B849FE}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4284,7 +4307,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{E977CA12-7C95-4E57-894A-0768785E4B72}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{012D0C57-DB6B-472C-8C7A-7B99DE29F70C}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4292,16 +4315,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{5140A975-6A60-4280-BCE4-6B97A4BAA3EC}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{861F0E55-0124-4ECB-92D6-9F41FB97502B}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{ABCF8B7A-FBDB-4E6C-BEA6-908DC8354C80}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{EC0ED3A6-5140-4267-AAAA-9AF78143F055}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{64A764CC-9EBF-4E70-88E8-EA1D64C310D4}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{9E085043-DFE7-447D-9B2E-BDA042A0E18C}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{94CC1A4B-3582-43CC-86D9-A0C469CEAF18}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{8259155F-58B2-44CC-8787-C0D86256A224}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5881,57 +5904,57 @@
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="F47 E200 F210">
-    <cfRule type="cellIs" dxfId="10" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F126:F127">
-    <cfRule type="cellIs" dxfId="9" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F138:F139">
-    <cfRule type="cellIs" dxfId="8" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F150:F151">
-    <cfRule type="cellIs" dxfId="7" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F162:F163">
-    <cfRule type="cellIs" dxfId="6" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F250:F251">
-    <cfRule type="cellIs" dxfId="5" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F255:F256">
-    <cfRule type="cellIs" dxfId="4" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F260:F261">
-    <cfRule type="cellIs" dxfId="3" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F284:F285">
-    <cfRule type="cellIs" dxfId="2" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F289:F290">
-    <cfRule type="cellIs" dxfId="1" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F294:F295">
-    <cfRule type="cellIs" dxfId="0" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6439,7 +6462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BDDFF2-3D95-47BA-886B-648B3235344C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A28648A-6E7B-4E65-9D29-0C4DFEC60D23}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10442,6 +10465,19 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMgAuADEAOgAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAyAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBRAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgACgAawBnACAAQwBPADIAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsAFwAbgAgACAAIAAgAFEAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMgAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFEAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBUAGkAdABsAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFUAbgBpAHQAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AUwBvAHUAcgBjAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -10636,19 +10672,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADIALgAxADoAIABTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMgAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AUQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AUQAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAIAB1AHMAZQBkACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAAoAGsAZwAgAEMATwAyACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEALABcAG4AIAAgACAAIABRACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADIALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBRAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAIAB1AHMAZQBkACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVABpAHQAbABlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBVAG4AaQB0ACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFMAbwB1AHIAYwBlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
@@ -10661,6 +10684,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10677,20 +10716,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/12_SupplementaryCO2_WIP_v02.xlsx
+++ b/Excel/12_SupplementaryCO2_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C137AC-7454-4E17-BE1C-4BC892D88E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC96DB31-0A5E-41EB-8A2B-3BC27DAF81AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15345" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15345" firstSheet="5" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Results" sheetId="13" r:id="rId3"/>
     <sheet name="Input - CO2 Use" sheetId="70" r:id="rId4"/>
     <sheet name="12.1.1-2 Supplementary CO2" sheetId="69" r:id="rId5"/>
-    <sheet name="Constants - Common" sheetId="123" r:id="rId6"/>
+    <sheet name="Constants - Common" sheetId="124" r:id="rId6"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId7"/>
@@ -38,7 +38,17 @@
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
-    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray,
+    _xlfn.XLOOKUP(
+        MEDIAN(
+            ROUND(_xlpm.Temperature, 0),
+            MIN(_xlpm.TemperatureArray),
+            MAX(_xlpm.TemperatureArray)
+        ),
+        _xlpm.TemperatureArray,
+        _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)
+    )
+)</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))))</definedName>
@@ -54,9 +64,28 @@
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse,
+    IFERROR(
+        _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1,
+            _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)
+        ),
+        IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)
+    )
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse,
+    _xlfn.XLOOKUP(1, (_xlpm.LookupArray1=_xlpm.LookupValue1)*(_xlpm.LookupArray2=_xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse))
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell,
+    SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) -1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell,
+  _xlfn.LET(
+    _xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"),
+    _xlpm.addr, CELL("address", _xlpm.TargetCell),
+    "#" &amp; _xlpm.addr
+  )
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -3875,16 +3904,16 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E54D8255-E094-4664-9B87-44EA918A7397}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{F7728B4F-8F44-465F-89E5-EF99C26E6C97}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5A8FDCE2-4C01-4CF4-BC13-5E791E7C1B87}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{85105BA8-F22C-4DFD-B7EC-E979DAAF5936}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{95C76E72-5256-4725-9123-CF12C4C2C13A}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{ACBBA79B-9B9E-4C65-8979-76E4D1737B2C}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3893,16 +3922,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{7513BCC0-3CAF-47DF-9CC1-D10B010D3C28}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{505602DE-AB74-4B66-97B3-A2826E0C870A}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{202B53AD-15AF-47DD-A8DF-8A644E1E62C2}" name="Data source">
+    <tableColumn id="1" xr3:uid="{09C0C5A5-FB8E-4C86-9127-DF32D2F40250}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{56455D86-FDA2-4D21-AC90-AAB3B6C4A12A}" name="Data score">
+    <tableColumn id="2" xr3:uid="{CA5CC6BB-C2C8-4606-B916-3425B4DC71A4}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3911,16 +3940,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{1DA84CC2-969F-41AE-9031-F99AD7852ABE}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{04C3F49A-A61E-4380-80A3-AF535E346EEE}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00A4B6C2-5609-43F5-98E4-4C50DC98E37A}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{21E905BC-7B4A-445F-B217-BA889B8C0C55}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{536575A5-4C36-45FD-B79B-7400C0B9097C}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{E5E6357B-688F-4070-AACE-D2F3C59D17A3}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3929,7 +3958,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{D662381A-BA07-49B3-98AC-156A7BC6DB24}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{A03704B9-3820-41A4-B30F-B690A9833663}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3938,19 +3967,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9C35C0F7-9728-46BB-B8F2-861D1557228C}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{7631AAF1-63C9-491F-8869-950320A9D3F1}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AF2525F5-AE3A-4F30-A43F-DAEC57F9BBBE}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{65935606-47D0-4651-9F14-A5EA3793C707}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2D59F631-206A-4B3A-925D-F801963D169B}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{3381328B-77CD-42B4-A52A-8227547334A5}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{29AA31B1-70D1-4F51-9B50-B0765353B3A1}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{E5594B0D-4109-4CC3-BB8B-2FD80DCF29FE}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5A43BDFF-85B3-4F71-847E-5291DB5FB039}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{FF10DBCE-03EB-4C9E-8EFC-2C3B57670810}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3959,16 +3988,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{DB17A14E-10C5-4ECB-8834-F42DCFB7B612}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{6483B135-B9BD-4C78-BB84-32DB3D8905EC}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2431C1A1-DA37-4C90-989F-1D7ECC95BC95}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{177AFDC3-1286-426A-8BDB-E2E7A00296C0}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{32AD751C-A971-4F05-A222-D3ECFF8DEC07}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{C6161CCA-A300-4A35-9431-95D71E9D9ADD}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3977,16 +4006,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{20205C5F-34FE-4762-B6E7-EDB665BAFEAB}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{982656AA-4EB6-4B74-9CDA-A7E41EA6F70E}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4BA23BF7-05DB-42D9-8B63-E3D6685CB1B2}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{BEC3DAE3-8C0A-478B-BBE1-C2A70F7C08F8}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{40309036-E4B2-49D7-8237-CF8693A73A8D}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{58F8C034-AC25-4D5A-8114-814A44079F74}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3995,16 +4024,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{44A964C5-1B1A-4810-B29D-22E4827F6D80}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{6D9F6660-EADC-4526-B5FE-EDF49D0D165F}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B326F2AA-58A8-4340-A737-DF7E207ADBB9}" name="Month">
+    <tableColumn id="1" xr3:uid="{AB41BD25-1F20-4A46-8A26-13A772FFFC0F}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A280D67F-3590-45D9-B7A7-DE06E7FC2CFC}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{0EA9D321-9A01-4BC9-8C44-34B47B56BCE5}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4013,7 +4042,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{94EFE41F-3966-48A0-AFCE-F4C9333145A1}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{3D7A3912-DF4A-4502-BD6F-47D34D4A8AED}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4033,52 +4062,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{0D3EBB1F-CBE3-4F48-943E-A8E5C14B79CE}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{588147A8-A244-42AF-A2D7-8CCFBC272F98}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3FD734E5-1A08-4F61-857C-89CB6A6BB7A4}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{0C7CEF3F-A32E-480D-B91B-5C0CB6D6304D}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B7E0A5A6-C943-41C8-9125-B0FD838AEEBB}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{84BDB2FA-B0DF-464A-9338-C743539E3C1E}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{9A9E2F12-4BC6-4014-8C09-0DC978B3D396}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{A4877172-5939-4D3B-8F08-CE68884D5E46}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{43A86789-1D5D-4506-99E5-2CE946C9B935}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{FEA834ED-7ABE-455B-88D6-EFD54ED3E564}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{FD6BD9E3-A536-4B32-BE04-8B2AA7D476FA}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{5E17DCD3-FC72-4AD3-ABBC-81A19765EBC7}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{08C13AA3-9ACE-4C3B-83E8-ED0D90040928}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{4D2357FC-AF2D-4DD0-A9D5-E442B4FF8CBF}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9D0A8979-2395-4107-AABD-6CF2A17A937E}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{5E2A9700-30E9-4366-BE1A-95DAD68470C8}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{77E2A6E4-4BFA-48D2-8683-A4E6221F80CC}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{E1B760CC-2D41-4D2A-9349-086319F7C554}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{3459A797-CF4F-4395-9C5A-5F7D164C0BB9}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{8979B28D-64E8-44EA-9267-91CECF7332BA}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{43506916-F6F4-42BB-B3D2-F163A8758B3F}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{3B188FA4-2A5A-4B85-9E1A-7CA7A1F46D92}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{09C53F63-61EA-431E-9466-AA55D1C98A41}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{81CBCC08-F709-4102-85DE-EC4953302CB8}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{3C68D010-20B5-4E85-AFD0-B6F35C274C96}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{87229DD8-88A4-49D1-983B-52E4A9493523}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{DF09420B-372D-4044-9824-6784C359E4FB}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{044F0AA8-E425-4EA3-8448-89701B4AD1EA}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{DD96BAF6-C820-4901-8631-684201BD37F1}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{83B85F80-B62D-4A08-9BC0-29E55D72A765}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{A9667774-9497-4E14-AD0B-1966CC5C78DB}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{1F5657B1-D96D-463B-AAD1-F49AF75E7C6E}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4087,16 +4116,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{47B9CC42-DAC1-4C7A-B36D-FFEEA3D02243}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{8AB29382-D3DB-4A04-ADED-3394CCA72508}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{EF4B9763-3A90-4CCB-BB06-7CB33C375183}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{5AE38991-6D40-4444-BDA1-3D6FE90BB4AC}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C86A6947-CC3E-449E-88B5-D3B85478E5FE}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1C22A2FE-0041-4BC4-8CE6-F194F387E14B}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4105,20 +4134,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DC9D5988-D4EF-4FA9-AD2F-7CE6809EDFC1}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0D8A2786-5250-469B-90A7-148F36C472FA}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A2551037-9F3E-40CA-8905-613EBF20DB28}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{21D4CA1C-CB19-469B-8049-F4B42EBA507C}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B7FFF453-85E6-452D-997C-0C2509DCDDE3}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{02AE3CA4-5932-488F-BF10-191312FBB893}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{99E7FA75-0DC9-4A64-8F09-67032DD4B825}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{AD3CA6C9-A92A-4E33-B2E4-C0058B87A5EC}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4127,12 +4156,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD482C2-2113-4569-A706-00AE921ED937}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1AB6CCF6-EFBB-4BBB-90C6-A3F51E4E672B}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{91A099A5-C097-4F07-A2C8-950B961AA2B7}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{A5CEEF1F-C6F8-42C3-97DF-323095B6639F}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4141,16 +4170,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3DF16CDD-F8A2-45EC-8A81-7CD614F61621}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{283B65D3-4E70-4403-804E-C4C73DDC484C}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{ED2625C0-E185-4A0A-935E-8967B5B41084}" name="Gas">
+    <tableColumn id="1" xr3:uid="{837DA029-D723-4655-9141-8837721AB1C8}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F358AFC6-BF6F-45EE-A0E5-FBE2D5E18CC6}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{42A592CA-97C1-48C8-9FDA-C3B325D31690}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4159,7 +4188,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C8E09135-8E20-48BF-B9F9-C4C2095F7DC4}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{2EFC5DBB-F1C5-4280-9592-7DE273B16672}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4168,19 +4197,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4FE22ACC-4AAE-4C9B-B5EC-31F585D9F514}" name="Gas">
+    <tableColumn id="1" xr3:uid="{9BD968AD-53FF-400F-8F0E-26C8C2B19441}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0B973D01-51E4-42EA-A52A-7B370A9818FC}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{7CBA6391-2A79-42A3-8A28-6F21314EC464}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1F60FF1E-475F-4C25-9951-5CE5CBEF269B}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{153F75EE-9D09-4908-A2B2-5172B254B0E5}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8A7A8DC6-1820-4468-98B3-8DC8D298768B}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{94D43728-567E-4277-A558-66E09A7180C7}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{AB15569A-614B-4A65-B948-7F3332198BB8}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{649BF81B-F26F-4CB1-9F4A-0A0C1E1F50F4}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4189,7 +4218,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{32C3ED2B-152D-48F1-BD54-D2E7DC0CEC3A}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{0AF546AC-F8F6-44B5-97A1-12C6FF382119}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4209,52 +4238,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{29BADEE5-11FA-482B-8555-5701BD405E33}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{ACD490F5-5BA4-44C7-8AA2-21F2C8CF85F3}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7B9180E5-E72F-41EB-8639-876A4B66BD50}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{2C40B810-911E-4094-828E-3D33DB1B1C16}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{FB64BEF6-3E4E-41A2-B49B-B6B5039D2DAF}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{5869FE5B-06C5-4CA8-BE10-46B1CBD82423}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{78FC67DC-FA57-436B-9821-A52723702DA2}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{5E97F5E4-955E-4B36-A4FB-C69415DF8D8D}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{2E77B52E-83BC-4C1B-8C1D-472000219827}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{957D91DB-5D8E-492C-9875-50BDFDA96F53}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{682EB6DE-3ADC-483A-8C67-11B2C9AD83CF}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{C6D0B56A-7709-438D-BBA6-801333813E63}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{90C582E0-AD24-4ED3-9051-0AF1809B4DB6}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{55E4F22F-F6A8-4FFD-B901-9B9D8EBB6696}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{899D33BD-3A3E-48DB-9B14-F8F785E5EC56}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{C461C64E-AAEB-4060-BD8F-6AAB52420F1B}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{D8493FFC-C1C4-428A-AF00-32143804CCAE}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{EB84BE5C-555C-412A-883E-1E8044173AB6}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{BB2B90DB-7CFB-481C-9BB1-9F0983BCF825}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{F4AC1218-A0EA-43C8-AB33-10FE0B427178}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{FF6EC65F-302D-4D95-97C2-143526B36E50}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{A6AE8BF2-3FAF-44BD-8E3E-C8FE2993117A}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{BD8B3749-226C-46EC-9FAC-9DFD01016A66}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{4E00CBCC-CFAF-4B50-BEE1-FBA6E2286E1E}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{5CA7B685-E4FF-415B-A071-D0565D4A0EC8}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{00801497-26D3-40E5-BF6C-1909140D6A66}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{703E4251-9F9A-4B5A-BDA7-EAFE87B2C251}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{E5FB0902-A43A-4E3F-BD06-1F3C3E410154}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{4299A7B8-62B9-439D-BE3B-86DDAC9BA7B1}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{AEBF902B-E74E-42FD-B53B-86763B597623}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{C7475492-A172-45FC-9D9B-8A2620899F29}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{26332127-A0B6-4003-8A15-C5D6BABB477D}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4263,16 +4292,16 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{95D2B30B-FDE4-4FCB-83C5-CC122F14B9EE}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{913DD6D9-C9E6-46AA-B205-297C7C13BB87}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{BDBE3A82-F5AB-4601-A9EC-1B58C33B4F9E}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{584D086E-6B08-4139-BA68-BB9E1C6F8E97}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{638CECC6-89F0-48CD-A20C-DEC3B9BF96DB}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{C34E6E37-39CD-49C3-9F57-F205AAC7E646}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4281,7 +4310,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{378BFE60-DACD-4546-9B8C-953262FD5EC6}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{CE8FC315-F066-4CFE-933D-F49E2241845E}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4289,16 +4318,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{3561C04F-8337-466E-8CF1-60DEFADEC820}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{2A28551F-FFCD-4B62-BBAE-E7177D570150}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0DE9DF78-83AF-4C11-8570-5EFA5B2B38AA}" name="MAT">
+    <tableColumn id="2" xr3:uid="{7641C49B-B056-4166-A5D8-1BDDB42AF136}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BD531263-84ED-4EF0-853E-FA6AAFCE4568}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{0704399A-8F52-4F22-9151-BBE5F47B3A40}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{14E0F267-CF46-4C14-80CD-850A36B849FE}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{3D4DF8FC-493D-4238-B5B2-2210DDD40E5F}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4307,7 +4336,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{012D0C57-DB6B-472C-8C7A-7B99DE29F70C}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{D06B152F-14A1-48B3-AD24-D0D11890F0A3}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4315,16 +4344,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{861F0E55-0124-4ECB-92D6-9F41FB97502B}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{96C94075-9A08-413B-A01A-92244FA8209C}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EC0ED3A6-5140-4267-AAAA-9AF78143F055}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{A209B906-1E7F-4DAC-99F8-2B393F70AE46}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9E085043-DFE7-447D-9B2E-BDA042A0E18C}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{DCC1FC76-6678-4128-99E9-2DFC2EDF8BE0}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8259155F-58B2-44CC-8787-C0D86256A224}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{8F6E20D9-1AA1-487E-82A8-0D073EF9337B}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6462,7 +6491,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A28648A-6E7B-4E65-9D29-0C4DFEC60D23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EBE29F2-4DAB-479B-BD33-74D7AFACAD09}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10454,21 +10483,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMgAuADEAOgAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAyAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBRAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgACgAawBnACAAQwBPADIAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsAFwAbgAgACAAIAAgAFEAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMgAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFEAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBUAGkAdABsAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFUAbgBpAHQAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AUwBvAHUAcgBjAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -10477,7 +10491,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -10672,26 +10686,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMgAuADEAOgAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAyAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBRAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgACgAawBnACAAQwBPADIAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsAFwAbgAgACAAIAAgAFEAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMgAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFEAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBUAGkAdABsAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFUAbgBpAHQAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AUwBvAHUAcgBjAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -10699,7 +10709,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10716,4 +10726,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Excel/12_SupplementaryCO2_WIP_v02.xlsx
+++ b/Excel/12_SupplementaryCO2_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC96DB31-0A5E-41EB-8A2B-3BC27DAF81AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F68347-82B0-4783-BFE1-E6372EEC1A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15345" firstSheet="5" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" firstSheet="5" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -18,11 +18,8 @@
     <sheet name="Results" sheetId="13" r:id="rId3"/>
     <sheet name="Input - CO2 Use" sheetId="70" r:id="rId4"/>
     <sheet name="12.1.1-2 Supplementary CO2" sheetId="69" r:id="rId5"/>
-    <sheet name="Constants - Common" sheetId="124" r:id="rId6"/>
+    <sheet name="Constants - Common" sheetId="125" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -329,10 +326,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="98">
-  <si>
-    <t>Home</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="97">
   <si>
     <t>INPUTS</t>
   </si>
@@ -869,13 +863,6 @@
       <family val="1"/>
     </font>
     <font>
-      <i/>
-      <sz val="12"/>
-      <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF0070C0"/>
       <name val="Times New Roman"/>
@@ -974,6 +961,12 @@
       <b/>
       <sz val="16"/>
       <color theme="1" tint="0.24994659260841701"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1379,7 +1372,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="7">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="7">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="26" fillId="4" borderId="2">
@@ -1397,7 +1390,7 @@
     <xf numFmtId="4" fontId="26" fillId="4" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="4" borderId="0">
+    <xf numFmtId="0" fontId="40" fillId="4" borderId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="0" applyNumberFormat="0">
@@ -1425,36 +1418,36 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="4" borderId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="4" borderId="0">
+    <xf numFmtId="0" fontId="41" fillId="4" borderId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="4" borderId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="14" borderId="2">
+    <xf numFmtId="0" fontId="43" fillId="14" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="15" borderId="2">
+    <xf numFmtId="0" fontId="42" fillId="15" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="2">
+    <xf numFmtId="0" fontId="44" fillId="4" borderId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="31" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -1487,22 +1480,16 @@
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="31">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="33">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="4" xfId="34">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="4" xfId="34" applyFont="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="9" borderId="4" xfId="34" applyFont="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="7" xfId="39">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="7" xfId="39">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -1536,38 +1523,35 @@
     <xf numFmtId="0" fontId="33" fillId="4" borderId="0" xfId="54">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="33" applyFont="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="32"/>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="9" xfId="39" applyBorder="1">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="9" xfId="39" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="11" xfId="39" applyBorder="1">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="11" xfId="39" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="12" xfId="39" applyBorder="1">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="12" xfId="39" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="13" xfId="39" applyBorder="1">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="13" xfId="39" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="53" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="4" borderId="0" xfId="59">
+    <xf numFmtId="0" fontId="41" fillId="4" borderId="0" xfId="59">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="24" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="11" borderId="0" xfId="60">
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="0" xfId="60">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="4" borderId="0" xfId="8" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="8" xfId="39" applyBorder="1">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="8" xfId="39" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="36">
@@ -1581,7 +1565,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="14" borderId="2" xfId="62">
+    <xf numFmtId="0" fontId="43" fillId="14" borderId="2" xfId="62">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="4" borderId="0" xfId="8" applyAlignment="1">
@@ -1590,9 +1574,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="2" xfId="65">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1602,11 +1583,10 @@
     <xf numFmtId="0" fontId="26" fillId="4" borderId="6" xfId="65" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="66"/>
     <xf numFmtId="169" fontId="8" fillId="4" borderId="0" xfId="10" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="9" borderId="0" xfId="32" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="46" fillId="9" borderId="0" xfId="32" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="31" fillId="9" borderId="0" xfId="8" applyFill="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1614,7 +1594,7 @@
     <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="31" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="13" borderId="10" xfId="39" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="10" xfId="39" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="37">
@@ -1623,26 +1603,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="15" xfId="39" applyBorder="1">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="15" xfId="39" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="14" xfId="39" applyBorder="1">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="14" xfId="39" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="16" xfId="39" applyBorder="1">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="16" xfId="39" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="14">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="4" borderId="1" xfId="8" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="49" fillId="4" borderId="1" xfId="8" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="4" borderId="1" xfId="8" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="1" xfId="8" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="4" borderId="1" xfId="53" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="1" xfId="53" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="9" borderId="4" xfId="34" applyFont="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" xfId="35">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="67">
@@ -1715,6 +1701,197 @@
     <cellStyle name="Variable type other" xfId="63" xr:uid="{6646F6F7-E4F9-4165-8015-E25083532B5B}"/>
   </cellStyles>
   <dxfs count="62">
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1" tint="0.14999847407452621"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0" tint="-5.0965910824915313E-2"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2576,197 +2753,6 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1" tint="0.249977111117893"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1" tint="0.14999847407452621"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0" tint="-5.0965910824915313E-2"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3805,26 +3791,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Constants - Common"/>
-      <sheetName val="Acknowledgements"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -3890,30 +3856,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6E44059A-C219-4316-A7A0-AD77B0121F06}" name="Table_Input_SupplementaryCO2" displayName="Table_Input_SupplementaryCO2" ref="D9:E11" totalsRowDxfId="49" headerRowCellStyle="Input table column header">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6E44059A-C219-4316-A7A0-AD77B0121F06}" name="Table_Input_SupplementaryCO2" displayName="Table_Input_SupplementaryCO2" ref="D9:E11" totalsRowDxfId="13" headerRowCellStyle="Input table column header">
   <autoFilter ref="D9:E11" xr:uid="{6E44059A-C219-4316-A7A0-AD77B0121F06}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="2" xr3:uid="{9540E705-999C-466B-A6B4-24C60E9153AE}" name="Usage description" totalsRowFunction="average" totalsRowDxfId="48" dataCellStyle="Input text" totalsRowCellStyle="Input select"/>
-    <tableColumn id="4" xr3:uid="{9DFFE0DC-C289-47FB-8F0C-2D2F480EEE4C}" name="Amount used (kg)" totalsRowDxfId="47" totalsRowCellStyle="Content bold"/>
+    <tableColumn id="2" xr3:uid="{9540E705-999C-466B-A6B4-24C60E9153AE}" name="Usage description" totalsRowFunction="average" totalsRowDxfId="12" dataCellStyle="Input text" totalsRowCellStyle="Input select"/>
+    <tableColumn id="4" xr3:uid="{9DFFE0DC-C289-47FB-8F0C-2D2F480EEE4C}" name="Amount used (kg)" totalsRowDxfId="11" totalsRowCellStyle="Content bold"/>
   </tableColumns>
   <tableStyleInfo name="Editable table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{F7728B4F-8F44-465F-89E5-EF99C26E6C97}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{EA1B28D0-5CF7-45DC-9091-9E7F742F94CB}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{85105BA8-F22C-4DFD-B7EC-E979DAAF5936}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{86785BC1-C012-4A20-B8A6-EF2D612D8574}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{ACBBA79B-9B9E-4C65-8979-76E4D1737B2C}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{1CA46F84-6C17-466B-95B4-0C7081DE3647}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3922,16 +3888,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{505602DE-AB74-4B66-97B3-A2826E0C870A}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{1C24D8BF-B7A8-4A5B-8903-B50A7F9A2D95}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{09C0C5A5-FB8E-4C86-9127-DF32D2F40250}" name="Data source">
+    <tableColumn id="1" xr3:uid="{CA25B0A3-4E27-47E9-B867-8842B0FCA9FA}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CA5CC6BB-C2C8-4606-B916-3425B4DC71A4}" name="Data score">
+    <tableColumn id="2" xr3:uid="{AC56093C-6B36-47FF-9BE1-C2EB40AEBEBC}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3940,16 +3906,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{04C3F49A-A61E-4380-80A3-AF535E346EEE}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{7C24474F-9170-4FB6-AF27-6C8C13C56624}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{21E905BC-7B4A-445F-B217-BA889B8C0C55}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{9C8C9774-9486-4AD8-95DA-1102815353B3}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E5E6357B-688F-4070-AACE-D2F3C59D17A3}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{4E798D23-EDBE-4D8C-B373-7E50178626CE}" name="FracWET" dataDxfId="33">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3958,7 +3924,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{A03704B9-3820-41A4-B30F-B690A9833663}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{83041A6F-6B0F-4A02-A259-CCD001D2F82D}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3967,19 +3933,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7631AAF1-63C9-491F-8869-950320A9D3F1}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{F7B9B734-A091-4922-9F7C-04E57048CC0D}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{65935606-47D0-4651-9F14-A5EA3793C707}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{A78EAFD0-9001-4EF1-ABCF-8577492D6A98}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{3381328B-77CD-42B4-A52A-8227547334A5}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{0F67F2E2-C61F-486B-B1ED-F5A8FCA0F36E}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E5594B0D-4109-4CC3-BB8B-2FD80DCF29FE}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{A3A30D71-F121-4844-9BC1-A974DB571E45}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FF10DBCE-03EB-4C9E-8EFC-2C3B57670810}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{17465E62-3630-4EDA-8DDA-8AFC21D06201}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3988,16 +3954,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{6483B135-B9BD-4C78-BB84-32DB3D8905EC}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{9D7EDD7F-CB0E-483C-9575-56C6283E357A}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{177AFDC3-1286-426A-8BDB-E2E7A00296C0}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{026F383A-0884-4558-93B5-5D7C74F400DA}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C6161CCA-A300-4A35-9431-95D71E9D9ADD}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{28933983-5B8F-497D-BB63-F14D64C60FCD}" name="FracWET" dataDxfId="32" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4006,16 +3972,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{982656AA-4EB6-4B74-9CDA-A7E41EA6F70E}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{24E0C0C7-2C05-4FF5-844C-58B028D51430}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{BEC3DAE3-8C0A-478B-BBE1-C2A70F7C08F8}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{D476228F-699A-41FF-BA3C-F69E45046819}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{58F8C034-AC25-4D5A-8114-814A44079F74}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{92D6952F-30B1-467C-AF65-C798E62E399B}" name="EFPRP" dataDxfId="31" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4024,16 +3990,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{6D9F6660-EADC-4526-B5FE-EDF49D0D165F}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{FC6653A4-B015-4CDF-9D37-49A4868CFA62}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AB41BD25-1F20-4A46-8A26-13A772FFFC0F}" name="Month">
+    <tableColumn id="1" xr3:uid="{17BE1E15-9AFE-410A-872A-C6E986222A18}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0EA9D321-9A01-4BC9-8C44-34B47B56BCE5}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{7D30E445-9EAB-4D48-9F7E-F0541A917A7D}" name="Season" dataDxfId="30" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4042,7 +4008,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{3D7A3912-DF4A-4502-BD6F-47D34D4A8AED}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{EA993081-BD8D-4099-996F-31FCD0252D86}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4062,52 +4028,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{588147A8-A244-42AF-A2D7-8CCFBC272F98}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{A84FFF7F-53F4-4C9B-81BA-81D74DEBD5FB}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0C7CEF3F-A32E-480D-B91B-5C0CB6D6304D}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F75BBDB3-B8FC-4775-980A-526DD6A95A84}" name="MAT (ºC)" dataDxfId="29" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{84BDB2FA-B0DF-464A-9338-C743539E3C1E}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{A8593797-A356-436E-8080-D452A846A26C}" name="Anaerobic lagoon" dataDxfId="28" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A4877172-5939-4D3B-8F08-CE68884D5E46}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{55728640-1F13-4F5E-926C-94480316D57D}" name="Digester / covered lagoons" dataDxfId="27" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FEA834ED-7ABE-455B-88D6-EFD54ED3E564}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{212F2380-25E8-4C76-8E57-41CEBACE1F9E}" name="Liquid systems" dataDxfId="26" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{5E17DCD3-FC72-4AD3-ABBC-81A19765EBC7}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{DAD75C42-8278-4D8E-AE3F-06BD2940119F}" name="Daily spread" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{4D2357FC-AF2D-4DD0-A9D5-E442B4FF8CBF}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{513F6B42-E3BB-4537-87D3-F1AE0D3DACED}" name="Composting (passive windrow)" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{5E2A9700-30E9-4366-BE1A-95DAD68470C8}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{2B95D6ED-DBCB-4D90-B52D-9D6E51D8F7AD}" name="Solid storage" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E1B760CC-2D41-4D2A-9349-086319F7C554}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{81FBF1EE-2B5E-40AE-926E-AD49F09B7100}" name="Pit storage" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{8979B28D-64E8-44EA-9267-91CECF7332BA}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{6EB40119-D2F6-4BAC-82AB-4FC43521F785}" name="Deep litter" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{3B188FA4-2A5A-4B85-9E1A-7CA7A1F46D92}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{0AEAEC45-28E0-46BB-8B03-9539ED62470B}" name="Poultry manure with bedding" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{81CBCC08-F709-4102-85DE-EC4953302CB8}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{56F9B960-6A79-4CD2-B4A5-0BA8992323A5}" name="Poultry manure without bedding" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{87229DD8-88A4-49D1-983B-52E4A9493523}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{A99C51A2-9907-4D37-835B-034DB1FD2C2D}" name="Direct processing" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{044F0AA8-E425-4EA3-8448-89701B4AD1EA}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{9CD1760C-CF26-49C0-A9B7-68DAFE16705A}" name="Direct application" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{83B85F80-B62D-4A08-9BC0-29E55D72A765}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{6A8430C4-FF3F-4976-BE36-116D83EBAD6A}" name="Pasture range and paddock" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{1F5657B1-D96D-463B-AAD1-F49AF75E7C6E}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{3FCA0DFC-16C0-4426-9001-0D949F41412D}" name="MAT raw" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4116,16 +4082,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{8AB29382-D3DB-4A04-ADED-3394CCA72508}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{FF51270D-20E5-40DF-A481-0D32B99BA07D}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5AE38991-6D40-4444-BDA1-3D6FE90BB4AC}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{58AE6CF3-779E-4AEE-AB9A-41AF7AF42C0C}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1C22A2FE-0041-4BC4-8CE6-F194F387E14B}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{C4E0EE74-8FD5-4AD8-AAA8-66DF13A6C347}" name="EFNi &amp; EFN2Oi" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4134,20 +4100,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0D8A2786-5250-469B-90A7-148F36C472FA}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CAFEEFC2-80D0-456B-B8C8-497FF24173BC}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{21D4CA1C-CB19-469B-8049-F4B42EBA507C}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{E6B1B569-AAB1-46E6-9DDE-4D74A2B1D199}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{02AE3CA4-5932-488F-BF10-191312FBB893}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{93F9A4DC-1C15-42AE-872B-FB8C7F0E2F78}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{AD3CA6C9-A92A-4E33-B2E4-C0058B87A5EC}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{3A52558C-6C93-4FA6-8C9B-4188610AD49E}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4156,12 +4122,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1AB6CCF6-EFBB-4BBB-90C6-A3F51E4E672B}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DE07724F-F8E7-4298-9B15-AE87513224ED}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{A5CEEF1F-C6F8-42C3-97DF-323095B6639F}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{7B0BAC61-71E9-4967-9127-116E7E15FE3D}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4170,16 +4136,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{283B65D3-4E70-4403-804E-C4C73DDC484C}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{95471A3E-5BBF-40E3-B2F8-4070E8A5685E}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{837DA029-D723-4655-9141-8837721AB1C8}" name="Gas">
+    <tableColumn id="1" xr3:uid="{3CDA1FA6-2A5A-4DEB-BC9B-B9E1DA90310E}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{42A592CA-97C1-48C8-9FDA-C3B325D31690}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{10C5059F-58ED-4A19-8504-CD901A13688B}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4188,7 +4154,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{2EFC5DBB-F1C5-4280-9592-7DE273B16672}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8A5A8414-DF6C-4FBA-B914-490134DBB0D6}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4197,19 +4163,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9BD968AD-53FF-400F-8F0E-26C8C2B19441}" name="Gas">
+    <tableColumn id="1" xr3:uid="{9CFE31AA-9854-40B7-9CAC-FB5D8F7BED2D}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7CBA6391-2A79-42A3-8A28-6F21314EC464}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{53DB137E-7605-4C79-BF7C-6AC4A9E632D3}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{153F75EE-9D09-4908-A2B2-5172B254B0E5}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{B6A24623-F6FF-4D84-A9D8-828E54C84871}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{94D43728-567E-4277-A558-66E09A7180C7}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{C1E58CB0-AF92-4DDC-85D7-DEB72E83FFB6}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{649BF81B-F26F-4CB1-9F4A-0A0C1E1F50F4}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{9797A665-1A7C-4758-9D0B-A346287440BC}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4218,7 +4184,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{0AF546AC-F8F6-44B5-97A1-12C6FF382119}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{09509B68-7F8C-4E6D-9A0D-0046BC2F9202}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4238,52 +4204,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{ACD490F5-5BA4-44C7-8AA2-21F2C8CF85F3}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{1218BD68-72AC-4B66-9D99-D24AC5B8C11A}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2C40B810-911E-4094-828E-3D33DB1B1C16}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{F1321AFC-2862-41D1-88EE-2701D37F412E}" name="MAT" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5869FE5B-06C5-4CA8-BE10-46B1CBD82423}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{D01D9811-E78E-4D13-AC68-9C4AB818B404}" name="MAP" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5E97F5E4-955E-4B36-A4FB-C69415DF8D8D}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{86B22D7A-84E6-4043-A7A9-73788E7095DE}" name="Frost days per year" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{957D91DB-5D8E-492C-9875-50BDFDA96F53}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{42EE899C-B3CA-4A3E-9776-99D0EDB85C3C}" name="Elevation" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{C6D0B56A-7709-438D-BBA6-801333813E63}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{29A29277-FCA8-4F9D-BD81-F0876FB398BE}" name="MAP:PET" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{55E4F22F-F6A8-4FFD-B901-9B9D8EBB6696}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{6B62BF03-F9B3-4F17-97F3-A96BE35E70CD}" name="Min temp" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{C461C64E-AAEB-4060-BD8F-6AAB52420F1B}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{29E94D1D-E462-4905-8645-8C16121FAE68}" name="Max temp" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{EB84BE5C-555C-412A-883E-1E8044173AB6}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{804AD3AE-F1C2-4A49-BC0B-E9F5DD3E9E91}" name="Min rainfall" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F4AC1218-A0EA-43C8-AB33-10FE0B427178}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{DAEB7BA1-A491-4E49-874D-F8BAD0471A78}" name="Max rainfall" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{A6AE8BF2-3FAF-44BD-8E3E-C8FE2993117A}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{6B7E653E-F918-4553-B91F-A95E53DBAC3F}" name="Min frost days" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{4E00CBCC-CFAF-4B50-BEE1-FBA6E2286E1E}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{80791DE2-3A9D-477F-862F-2BE6396DF726}" name="Max frost days" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00801497-26D3-40E5-BF6C-1909140D6A66}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{F9513656-161B-45C6-924A-F9DFDAFD9F7C}" name="Min elevation" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{E5FB0902-A43A-4E3F-BD06-1F3C3E410154}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{B8DFA4ED-D19C-4801-843F-43156C580EE6}" name="Max elevation" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{AEBF902B-E74E-42FD-B53B-86763B597623}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{E4480FB7-7DE7-4E2B-9867-F1A5757705F6}" name="Min MAP:PET" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{26332127-A0B6-4003-8A15-C5D6BABB477D}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{E0EE92EB-0DD5-49DE-971B-C61313C52B8A}" name="Max MAP:PET" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4292,16 +4258,16 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{913DD6D9-C9E6-46AA-B205-297C7C13BB87}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{816858F6-1550-4E05-869A-34CC57F0232E}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{584D086E-6B08-4139-BA68-BB9E1C6F8E97}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{9B8523F0-3DF1-4580-A2BD-62B299071E75}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C34E6E37-39CD-49C3-9F57-F205AAC7E646}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{90E4276C-A5A4-42ED-BCBE-071BD3F1AB33}" name="Wet or Dry Zone" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4310,7 +4276,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{CE8FC315-F066-4CFE-933D-F49E2241845E}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D47FBBFB-6A56-4D8F-B32E-6C3AF04EB59E}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4318,16 +4284,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2A28551F-FFCD-4B62-BBAE-E7177D570150}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{EA055807-8D44-4869-B261-797BB5FB54EA}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7641C49B-B056-4166-A5D8-1BDDB42AF136}" name="MAT">
+    <tableColumn id="2" xr3:uid="{0D2F2071-C82D-4675-B87A-0B4B02C17D75}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0704399A-8F52-4F22-9151-BBE5F47B3A40}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{94B6C14F-A507-4A79-ADC0-DD5CDC75CB22}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3D4DF8FC-493D-4238-B5B2-2210DDD40E5F}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{409AA55E-5A49-4426-8654-C9BE141EAB91}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4336,7 +4302,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{D06B152F-14A1-48B3-AD24-D0D11890F0A3}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9D7DC10B-CB0E-43F7-B841-F9727CC5CEB9}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4344,16 +4310,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{96C94075-9A08-413B-A01A-92244FA8209C}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{0D728E6B-B1C3-4B47-B1C6-A2DFF028507C}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A209B906-1E7F-4DAC-99F8-2B393F70AE46}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{82611AC2-615C-4624-A673-03883FD72A6F}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DCC1FC76-6678-4128-99E9-2DFC2EDF8BE0}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{D58C6494-60DB-4AD8-BEF9-52F5AD2642A5}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8F6E20D9-1AA1-487E-82A8-0D073EF9337B}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{41B78E65-3431-4BA3-BC89-26DBF324B243}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4616,12 +4582,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53CF26AA-F4FA-460F-9B3A-C19960195F0B}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:1" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="29" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="41" t="str">
+        <f>HYPERLINK("#'Home'!A1", "Home")</f>
+        <v>Home</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="str">
+        <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
+        <v>Overview</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="str">
+        <f>HYPERLINK("#'Results'!A1", "Results")</f>
+        <v>Results</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="str">
+        <f>HYPERLINK("#'Input - CO2 Use'!A1", "CO2 Use")</f>
+        <v>CO2 Use</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="str">
+        <f>HYPERLINK("#'12.1.1-2 Supplementary CO2'!A1", "12.1.1-2 Supplementary CO2")</f>
+        <v>12.1.1-2 Supplementary CO2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="65" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="str">
+        <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
+        <v>Constants - Common</v>
       </c>
     </row>
   </sheetData>
@@ -4642,159 +4659,152 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="e" vm="1">
+      <c r="A1" s="29" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C1" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
+      <c r="C1" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
     </row>
     <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="58"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="53"/>
     </row>
     <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="str">
+      <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="59"/>
-      <c r="L3" s="59"/>
-      <c r="M3" s="59"/>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="54"/>
     </row>
     <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="44" t="str">
+      <c r="A4" s="41" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="str">
+      <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="30"/>
+    </row>
+    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="33"/>
-    </row>
-    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="D6" s="60" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="34"/>
-    </row>
-    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>1</v>
-      </c>
-    </row>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="31"/>
+    </row>
+    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="str">
+      <c r="A8" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - CO2 Use'!A1", "CO2 Use")</f>
         <v>CO2 Use</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
-    </row>
-    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="str">
+    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'12.1.1-2 Supplementary CO2'!A1", "12.1.1-2 Supplementary CO2")</f>
         <v>12.1.1-2 Supplementary CO2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-    </row>
-    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>2</v>
-      </c>
-    </row>
     <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="str">
+      <c r="O14" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="65" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
-      <c r="O14" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
     <row r="18" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="20" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-    </row>
+    <row r="22" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4811,7 +4821,7 @@
     <row r="36" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L37" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4821,7 +4831,7 @@
     <row r="42" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="45" spans="12:23" x14ac:dyDescent="0.25">
       <c r="W45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -4847,767 +4857,760 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="e" vm="1">
+      <c r="A1" s="29" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C1" s="56" t="s">
-        <v>96</v>
+      <c r="C1" s="51" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
       <c r="C2" s="8"/>
     </row>
     <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="str">
+      <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="str">
+      <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
-      <c r="C4" s="18"/>
+      <c r="C4" s="16"/>
       <c r="D4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="20"/>
+        <v>2</v>
+      </c>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="18"/>
     </row>
     <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="44" t="str">
+      <c r="A5" s="41" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="18"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="16"/>
     </row>
     <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="str">
+      <c r="A8" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="16"/>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - CO2 Use'!A1", "CO2 Use")</f>
         <v>CO2 Use</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="18"/>
-    </row>
-    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
-      <c r="C9" s="18"/>
+      <c r="C9" s="16"/>
       <c r="D9" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="55">
+        <v>87</v>
+      </c>
+      <c r="E9" s="50">
         <f>VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2_Result_Method1</f>
         <v>0.2</v>
       </c>
-      <c r="F9" s="55">
+      <c r="F9" s="50">
         <f>E9</f>
         <v>0.2</v>
       </c>
-      <c r="G9" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="H9" s="18"/>
+      <c r="G9" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="16"/>
     </row>
     <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="39">
+      <c r="C10" s="16"/>
+      <c r="D10" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="36">
         <f>SUM(E9:E9)</f>
         <v>0.2</v>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="36">
         <f>SUM(F9:F9)</f>
         <v>0.2</v>
       </c>
-      <c r="G10" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="H10" s="18"/>
+      <c r="G10" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" s="16"/>
     </row>
     <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="str">
-        <f>HYPERLINK("#'12.1.1-2 Supplementary CO2'!A1", "12.1.1-2 Supplementary CO2")</f>
-        <v>12.1.1-2 Supplementary CO2</v>
-      </c>
-      <c r="C11" s="18"/>
+      <c r="C11" s="16"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="18"/>
+      <c r="H11" s="16"/>
     </row>
     <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="C12" s="18"/>
+      <c r="A12" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="16"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="18"/>
+      <c r="H12" s="16"/>
     </row>
     <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="18"/>
+      <c r="A13" s="12" t="str">
+        <f>HYPERLINK("#'12.1.1-2 Supplementary CO2'!A1", "12.1.1-2 Supplementary CO2")</f>
+        <v>12.1.1-2 Supplementary CO2</v>
+      </c>
+      <c r="C13" s="16"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="29"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="27"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="18"/>
+      <c r="H13" s="16"/>
     </row>
     <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="str">
-        <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
-        <v>Constants - Common</v>
-      </c>
-      <c r="C14" s="18"/>
+      <c r="C14" s="16"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="29"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="18"/>
+      <c r="H14" s="16"/>
     </row>
     <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="18"/>
+      <c r="C15" s="16"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="18"/>
+      <c r="H15" s="16"/>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="18"/>
+      <c r="A16" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="16"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="18"/>
+      <c r="H16" s="16"/>
     </row>
     <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="18"/>
+      <c r="A17" s="12" t="str">
+        <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
+        <v>Constants - Common</v>
+      </c>
+      <c r="C17" s="16"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
-      <c r="H17" s="18"/>
+      <c r="H17" s="16"/>
     </row>
     <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="18"/>
+      <c r="C18" s="16"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-      <c r="H18" s="18"/>
+      <c r="H18" s="16"/>
     </row>
     <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="18"/>
+      <c r="C19" s="16"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
-      <c r="H19" s="18"/>
+      <c r="H19" s="16"/>
     </row>
     <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="C20" s="18"/>
+      <c r="C20" s="16"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
-      <c r="H20" s="18"/>
+      <c r="H20" s="16"/>
     </row>
     <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="C21" s="18"/>
+      <c r="C21" s="16"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="29"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="27"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="18"/>
+      <c r="H21" s="16"/>
     </row>
     <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="18"/>
+      <c r="C22" s="16"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="29"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="27"/>
       <c r="G22" s="1"/>
-      <c r="H22" s="18"/>
+      <c r="H22" s="16"/>
     </row>
     <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="C23" s="18"/>
+      <c r="C23" s="16"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="18"/>
+      <c r="H23" s="16"/>
     </row>
     <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="18"/>
+      <c r="C24" s="16"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
-      <c r="H24" s="18"/>
+      <c r="H24" s="16"/>
     </row>
     <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="18"/>
+      <c r="C25" s="16"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="18"/>
+      <c r="H25" s="16"/>
     </row>
     <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="18"/>
+      <c r="C26" s="16"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="18"/>
+      <c r="H26" s="16"/>
     </row>
     <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="18"/>
+      <c r="C27" s="16"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="18"/>
+      <c r="H27" s="16"/>
     </row>
     <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="18"/>
+      <c r="C28" s="16"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="18"/>
+      <c r="H28" s="16"/>
     </row>
     <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="18"/>
+      <c r="C29" s="16"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="18"/>
+      <c r="H29" s="16"/>
     </row>
     <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="18"/>
+      <c r="C30" s="16"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="18"/>
+      <c r="H30" s="16"/>
     </row>
     <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="18"/>
+      <c r="C31" s="16"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="18"/>
+      <c r="H31" s="16"/>
     </row>
     <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="18"/>
+      <c r="C32" s="16"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
-      <c r="H32" s="18"/>
+      <c r="H32" s="16"/>
     </row>
     <row r="33" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="18"/>
+      <c r="C33" s="16"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
-      <c r="H33" s="18"/>
+      <c r="H33" s="16"/>
     </row>
     <row r="34" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="18"/>
+      <c r="C34" s="16"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="18"/>
+      <c r="H34" s="16"/>
     </row>
     <row r="35" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="18"/>
+      <c r="C35" s="16"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="H35" s="18"/>
+      <c r="H35" s="16"/>
     </row>
     <row r="36" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="18"/>
+      <c r="C36" s="16"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="18"/>
+      <c r="H36" s="16"/>
     </row>
     <row r="37" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="18"/>
+      <c r="C37" s="16"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="18"/>
+      <c r="H37" s="16"/>
     </row>
     <row r="38" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="18"/>
+      <c r="C38" s="16"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
-      <c r="H38" s="18"/>
+      <c r="H38" s="16"/>
     </row>
     <row r="39" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="18"/>
+      <c r="C39" s="16"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
-      <c r="H39" s="18"/>
+      <c r="H39" s="16"/>
     </row>
     <row r="40" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="18"/>
+      <c r="C40" s="16"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
-      <c r="H40" s="18"/>
+      <c r="H40" s="16"/>
     </row>
     <row r="41" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="18"/>
+      <c r="C41" s="16"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
-      <c r="H41" s="18"/>
+      <c r="H41" s="16"/>
     </row>
     <row r="42" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="18"/>
+      <c r="C42" s="16"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="18"/>
+      <c r="H42" s="16"/>
     </row>
     <row r="43" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="18"/>
+      <c r="C43" s="16"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
-      <c r="H43" s="18"/>
+      <c r="H43" s="16"/>
     </row>
     <row r="44" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="18"/>
+      <c r="C44" s="16"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
-      <c r="H44" s="18"/>
+      <c r="H44" s="16"/>
     </row>
     <row r="45" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="18"/>
+      <c r="C45" s="16"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
-      <c r="H45" s="18"/>
+      <c r="H45" s="16"/>
     </row>
     <row r="46" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="18"/>
+      <c r="C46" s="16"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
-      <c r="H46" s="18"/>
+      <c r="H46" s="16"/>
     </row>
     <row r="47" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="18"/>
+      <c r="C47" s="16"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
-      <c r="H47" s="18"/>
+      <c r="H47" s="16"/>
     </row>
     <row r="48" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C48" s="18"/>
+      <c r="C48" s="16"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
-      <c r="H48" s="18"/>
+      <c r="H48" s="16"/>
     </row>
     <row r="49" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C49" s="18"/>
+      <c r="C49" s="16"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="18"/>
+      <c r="H49" s="16"/>
     </row>
     <row r="50" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C50" s="18"/>
+      <c r="C50" s="16"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
-      <c r="H50" s="18"/>
+      <c r="H50" s="16"/>
     </row>
     <row r="51" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C51" s="18"/>
+      <c r="C51" s="16"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
-      <c r="H51" s="18"/>
+      <c r="H51" s="16"/>
     </row>
     <row r="52" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C52" s="18"/>
+      <c r="C52" s="16"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
-      <c r="H52" s="18"/>
+      <c r="H52" s="16"/>
     </row>
     <row r="53" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C53" s="18"/>
+      <c r="C53" s="16"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
-      <c r="H53" s="18"/>
+      <c r="H53" s="16"/>
     </row>
     <row r="54" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="18"/>
+      <c r="C54" s="16"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
-      <c r="H54" s="18"/>
+      <c r="H54" s="16"/>
     </row>
     <row r="55" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="18"/>
+      <c r="C55" s="16"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
-      <c r="H55" s="18"/>
+      <c r="H55" s="16"/>
     </row>
     <row r="56" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C56" s="18"/>
+      <c r="C56" s="16"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
-      <c r="H56" s="18"/>
+      <c r="H56" s="16"/>
     </row>
     <row r="57" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="18"/>
+      <c r="C57" s="16"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
-      <c r="H57" s="18"/>
+      <c r="H57" s="16"/>
     </row>
     <row r="58" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C58" s="18"/>
+      <c r="C58" s="16"/>
       <c r="D58" s="1"/>
-      <c r="E58" s="25"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="18"/>
-      <c r="H58" s="18"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="16"/>
+      <c r="H58" s="16"/>
     </row>
     <row r="59" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C59" s="18"/>
+      <c r="C59" s="16"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
-      <c r="H59" s="18"/>
+      <c r="H59" s="16"/>
     </row>
     <row r="60" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C60" s="18"/>
+      <c r="C60" s="16"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
-      <c r="H60" s="18"/>
+      <c r="H60" s="16"/>
     </row>
     <row r="61" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C61" s="18"/>
+      <c r="C61" s="16"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="18"/>
+      <c r="H61" s="16"/>
     </row>
     <row r="62" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C62" s="18"/>
+      <c r="C62" s="16"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
-      <c r="H62" s="18"/>
+      <c r="H62" s="16"/>
     </row>
     <row r="63" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C63" s="18"/>
+      <c r="C63" s="16"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
-      <c r="H63" s="18"/>
+      <c r="H63" s="16"/>
     </row>
     <row r="64" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="18"/>
+      <c r="C64" s="16"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
-      <c r="H64" s="18"/>
+      <c r="H64" s="16"/>
     </row>
     <row r="65" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="18"/>
+      <c r="C65" s="16"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
-      <c r="H65" s="18"/>
+      <c r="H65" s="16"/>
     </row>
     <row r="66" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="18"/>
+      <c r="C66" s="16"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
-      <c r="H66" s="18"/>
+      <c r="H66" s="16"/>
     </row>
     <row r="67" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="18"/>
+      <c r="C67" s="16"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
-      <c r="H67" s="18"/>
+      <c r="H67" s="16"/>
     </row>
     <row r="68" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="18"/>
+      <c r="C68" s="16"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
-      <c r="H68" s="18"/>
+      <c r="H68" s="16"/>
     </row>
     <row r="69" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="18"/>
+      <c r="C69" s="16"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
-      <c r="H69" s="18"/>
+      <c r="H69" s="16"/>
     </row>
     <row r="70" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C70" s="18"/>
+      <c r="C70" s="16"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
-      <c r="H70" s="18"/>
+      <c r="H70" s="16"/>
     </row>
     <row r="71" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C71" s="18"/>
+      <c r="C71" s="16"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
-      <c r="H71" s="18"/>
+      <c r="H71" s="16"/>
     </row>
     <row r="72" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C72" s="18"/>
+      <c r="C72" s="16"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
-      <c r="H72" s="18"/>
+      <c r="H72" s="16"/>
     </row>
     <row r="73" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C73" s="18"/>
+      <c r="C73" s="16"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
-      <c r="H73" s="18"/>
+      <c r="H73" s="16"/>
     </row>
     <row r="74" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C74" s="18"/>
+      <c r="C74" s="16"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
-      <c r="H74" s="18"/>
+      <c r="H74" s="16"/>
     </row>
     <row r="75" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C75" s="18"/>
+      <c r="C75" s="16"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
-      <c r="H75" s="18"/>
+      <c r="H75" s="16"/>
     </row>
     <row r="76" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C76" s="18"/>
+      <c r="C76" s="16"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
-      <c r="H76" s="18"/>
+      <c r="H76" s="16"/>
     </row>
     <row r="77" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C77" s="18"/>
+      <c r="C77" s="16"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
-      <c r="H77" s="18"/>
+      <c r="H77" s="16"/>
     </row>
     <row r="78" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C78" s="18"/>
+      <c r="C78" s="16"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
-      <c r="H78" s="18"/>
+      <c r="H78" s="16"/>
     </row>
     <row r="79" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C79" s="18"/>
+      <c r="C79" s="16"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
-      <c r="H79" s="18"/>
+      <c r="H79" s="16"/>
     </row>
     <row r="80" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C80" s="18"/>
+      <c r="C80" s="16"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
-      <c r="H80" s="18"/>
+      <c r="H80" s="16"/>
     </row>
     <row r="81" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C81" s="18"/>
+      <c r="C81" s="16"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
-      <c r="H81" s="18"/>
+      <c r="H81" s="16"/>
     </row>
     <row r="82" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C82" s="18"/>
+      <c r="C82" s="16"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
-      <c r="H82" s="18"/>
+      <c r="H82" s="16"/>
     </row>
     <row r="83" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C83" s="18"/>
+      <c r="C83" s="16"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
-      <c r="H83" s="18"/>
+      <c r="H83" s="16"/>
     </row>
     <row r="84" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C84" s="18"/>
+      <c r="C84" s="16"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
-      <c r="H84" s="18"/>
+      <c r="H84" s="16"/>
     </row>
     <row r="85" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C85" s="18"/>
+      <c r="C85" s="16"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
-      <c r="H85" s="18"/>
+      <c r="H85" s="16"/>
     </row>
     <row r="86" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C86" s="18"/>
-      <c r="D86" s="18"/>
-      <c r="E86" s="18"/>
-      <c r="F86" s="18"/>
-      <c r="G86" s="18"/>
-      <c r="H86" s="18"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="16"/>
+      <c r="E86" s="16"/>
+      <c r="F86" s="16"/>
+      <c r="G86" s="16"/>
+      <c r="H86" s="16"/>
     </row>
     <row r="87" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="18"/>
-      <c r="H87" s="18"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="16"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="16"/>
+      <c r="H87" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5629,17 +5632,19 @@
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="32" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="e" vm="1">
+    <row r="1" spans="1:7" s="29" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="29" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C1" s="32" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="C1" s="29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2"/>
+    </row>
     <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="str">
+      <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
@@ -5650,151 +5655,133 @@
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="str">
+      <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="str">
+      <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
     </row>
     <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="64" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" s="65"/>
-      <c r="F7" s="63"/>
+      <c r="D7" s="59" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="60"/>
+      <c r="F7" s="58"/>
     </row>
     <row r="8" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="43" t="str">
+      <c r="A8" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+    </row>
+    <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="40" t="str">
         <f>HYPERLINK("#'Input - CO2 Use'!A1", "CO2 Use")</f>
         <v>CO2 Use</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-    </row>
-    <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
-      <c r="D9" s="46" t="s">
+      <c r="D9" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="F9" s="16"/>
+    </row>
+    <row r="10" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D10" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="F9" s="18"/>
-    </row>
-    <row r="10" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="66" t="s">
+      <c r="E10" s="57">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D11" s="61" t="s">
         <v>91</v>
       </c>
-      <c r="E10" s="62">
+      <c r="E11" s="57">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="str">
+    <row r="12" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'12.1.1-2 Supplementary CO2'!A1", "12.1.1-2 Supplementary CO2")</f>
         <v>12.1.1-2 Supplementary CO2</v>
       </c>
-      <c r="D11" s="66" t="s">
-        <v>92</v>
-      </c>
-      <c r="E11" s="62">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-    </row>
-    <row r="13" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="str">
+    </row>
+    <row r="14" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="65" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-    </row>
-    <row r="21" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-    </row>
+    <row r="20" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-    </row>
+    <row r="23" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="13"/>
-    </row>
-    <row r="30" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
-    </row>
-    <row r="31" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="31"/>
-    </row>
-    <row r="32" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="31"/>
-    </row>
-    <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="13"/>
-    </row>
+    <row r="29" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="48"/>
-      <c r="G38" s="48"/>
+      <c r="C38" s="45"/>
+      <c r="G38" s="45"/>
     </row>
     <row r="39" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="13"/>
-      <c r="C39" s="48"/>
-      <c r="G39" s="48"/>
-    </row>
-    <row r="40" spans="1:7" s="49" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="45"/>
+      <c r="G39" s="45"/>
+    </row>
+    <row r="40" spans="1:7" s="46" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:7" s="49" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="50"/>
+    <row r="41" spans="1:7" s="46" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -5803,9 +5790,7 @@
     </row>
     <row r="42" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="54"/>
-    </row>
+    <row r="44" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="45" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="46" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5928,62 +5913,62 @@
     <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="351" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D351" s="38"/>
+      <c r="D351" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="F47 E200 F210">
-    <cfRule type="cellIs" dxfId="46" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F126:F127">
-    <cfRule type="cellIs" dxfId="45" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F138:F139">
-    <cfRule type="cellIs" dxfId="44" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F150:F151">
-    <cfRule type="cellIs" dxfId="43" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F162:F163">
-    <cfRule type="cellIs" dxfId="42" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F250:F251">
-    <cfRule type="cellIs" dxfId="41" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F255:F256">
-    <cfRule type="cellIs" dxfId="40" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F260:F261">
-    <cfRule type="cellIs" dxfId="39" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F284:F285">
-    <cfRule type="cellIs" dxfId="38" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F289:F290">
-    <cfRule type="cellIs" dxfId="37" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F294:F295">
-    <cfRule type="cellIs" dxfId="36" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6029,22 +6014,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="e" vm="1">
+      <c r="A1" s="29" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2"/>
+    </row>
     <row r="3" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="str">
+      <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -6060,13 +6047,13 @@
       <c r="P3" s="3"/>
     </row>
     <row r="4" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="str">
+      <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="str">
+      <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
       </c>
@@ -6074,152 +6061,145 @@
         <f t="array" ref="D5">SupplementaryCO2_Equations.VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2_Title()</f>
         <v>Emissions from the use of supplementary CO2</v>
       </c>
-      <c r="O5" s="45"/>
+      <c r="O5" s="42"/>
     </row>
     <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
       <c r="D6" s="4" t="str" cm="1">
         <f t="array" ref="D6">SupplementaryCO2_Equations.VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2_Source()</f>
         <v>VEERG 2026: 12.1.1.1, Equation (1)</v>
       </c>
-      <c r="O6" s="45"/>
+      <c r="O6" s="42"/>
     </row>
     <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>1</v>
-      </c>
       <c r="D7" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="E7" ca="1">Common_InputFunctions.Utility_DisplayFunctionName(E15)</f>
         <v>=SupplementaryCO2_Equations.VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2</v>
       </c>
-      <c r="O7" s="45"/>
+      <c r="O7" s="42"/>
     </row>
     <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="str">
+      <c r="A8" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O8" s="42"/>
+    </row>
+    <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - CO2 Use'!A1", "CO2 Use")</f>
         <v>CO2 Use</v>
       </c>
-      <c r="O8" s="45"/>
-    </row>
-    <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
       <c r="G9" s="4"/>
-      <c r="O9" s="45"/>
+      <c r="O9" s="42"/>
     </row>
     <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>13</v>
+      <c r="D10" s="26" t="s">
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="str" cm="1">
         <f t="array" ref="E10">SupplementaryCO2_Equations.VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2_Variable()</f>
         <v>E</v>
       </c>
-      <c r="O10" s="45"/>
+      <c r="O10" s="42"/>
     </row>
     <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="61" t="str">
+      <c r="D11" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="27" t="str" cm="1">
+        <f t="array" ref="E11">SupplementaryCO2_Equations.VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2_Unit()</f>
+        <v>t CO2e</v>
+      </c>
+      <c r="O11" s="42"/>
+    </row>
+    <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="56" t="str">
         <f>HYPERLINK("#'12.1.1-2 Supplementary CO2'!A1", "12.1.1-2 Supplementary CO2")</f>
         <v>12.1.1-2 Supplementary CO2</v>
       </c>
-      <c r="D11" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="29" t="str" cm="1">
-        <f t="array" ref="E11">SupplementaryCO2_Equations.VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2_Unit()</f>
-        <v>t CO2e</v>
-      </c>
-      <c r="O11" s="45"/>
-    </row>
-    <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-    </row>
-    <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="51" t="str" cm="1">
+      <c r="D13" s="47" t="str" cm="1">
         <f t="array" ref="D13:E13">_xlfn.CHOOSECOLS(SupplementaryCO2_Equations.VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2_Arguments(), 1,2)</f>
         <v>Q</v>
       </c>
-      <c r="E13" s="53" t="str">
+      <c r="E13" s="49" t="str">
         <v>quantity of supplementary CO2 used within the operations</v>
       </c>
-      <c r="F13" s="52"/>
-      <c r="G13" s="51" t="str" cm="1">
+      <c r="F13" s="48"/>
+      <c r="G13" s="47" t="str" cm="1">
         <f t="array" ref="G13:H13">_xlfn.CHOOSECOLS(SupplementaryCO2_Equations.VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2_Arguments(), 3,4)</f>
         <v>kg CO2</v>
       </c>
-      <c r="H13" s="47" t="str">
+      <c r="H13" s="44" t="str">
         <v>Input</v>
       </c>
-      <c r="I13" s="51">
+      <c r="I13" s="47">
         <f>SUM(Table_Input_SupplementaryCO2[Amount used (kg)])</f>
         <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="str">
+      <c r="O14" s="42"/>
+    </row>
+    <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D15" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="63" cm="1">
+        <f t="array" ref="E15">SupplementaryCO2_Equations.VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2(I13)</f>
+        <v>0.2</v>
+      </c>
+      <c r="F15" s="64" t="str">
+        <f>E11</f>
+        <v>t CO2e</v>
+      </c>
+      <c r="O15" s="42"/>
+    </row>
+    <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="O16" s="42"/>
+    </row>
+    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
-      <c r="O14" s="45"/>
-    </row>
-    <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" s="68" cm="1">
-        <f t="array" ref="E15">SupplementaryCO2_Equations.VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2(I13)</f>
-        <v>0.2</v>
-      </c>
-      <c r="F15" s="69" t="str">
-        <f>E11</f>
-        <v>t CO2e</v>
-      </c>
-      <c r="O15" s="45"/>
-    </row>
-    <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O16" s="45"/>
-    </row>
-    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L17" s="45"/>
-      <c r="M17" s="45"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="45"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="42"/>
     </row>
     <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="45"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="42"/>
     </row>
     <row r="19" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L19" s="45"/>
-      <c r="M19" s="45"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="45"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="42"/>
     </row>
     <row r="20" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="L20" s="45"/>
-      <c r="M20" s="45"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="45"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
     </row>
     <row r="21" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="O21" s="45"/>
+      <c r="O21" s="42"/>
     </row>
     <row r="22" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-    </row>
+    <row r="23" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6229,24 +6209,22 @@
     <row r="30" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="54"/>
-    </row>
-    <row r="38" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6263,42 +6241,38 @@
     <row r="62" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="54"/>
-    </row>
-    <row r="70" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="54"/>
-    </row>
-    <row r="84" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6475,10 +6449,10 @@
     <row r="270" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="271" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="341" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H341" s="18"/>
+      <c r="H341" s="16"/>
     </row>
     <row r="342" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H342" s="18"/>
+      <c r="H342" s="16"/>
     </row>
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
@@ -6491,7 +6465,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EBE29F2-4DAB-479B-BD33-74D7AFACAD09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA18C4B-3632-4910-83EB-896E1D677F48}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6519,16 +6493,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:65" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="e" vm="1">
+      <c r="A1" s="29" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:65" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:65" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2"/>
+    </row>
     <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3"/>
+      <c r="A3" s="12" t="str">
+        <f>HYPERLINK("#'Home'!A1", "Home")</f>
+        <v>Home</v>
+      </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -6552,11 +6531,17 @@
       <c r="W3" s="9"/>
     </row>
     <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4"/>
+      <c r="A4" s="12" t="str">
+        <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
+        <v>Overview</v>
+      </c>
       <c r="BM4" s="2"/>
     </row>
     <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5"/>
+      <c r="A5" s="12" t="str">
+        <f>HYPERLINK("#'Results'!A1", "Results")</f>
+        <v>Results</v>
+      </c>
       <c r="D5" s="5" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
         <v>Australian states and territories</v>
@@ -6565,134 +6550,144 @@
     </row>
     <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6"/>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="F6" s="25" t="s">
         <v>7</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7"/>
-      <c r="D7" s="27" t="str" cm="1">
+      <c r="D7" s="25" t="str" cm="1">
         <f t="array" ref="D7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>New South Wales</v>
       </c>
-      <c r="E7" s="27" t="str" cm="1">
+      <c r="E7" s="25" t="str" cm="1">
         <f t="array" ref="E7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>New South Wales</v>
       </c>
-      <c r="F7" s="27" t="str" cm="1">
+      <c r="F7" s="25" t="str" cm="1">
         <f t="array" ref="F7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>NSW</v>
       </c>
     </row>
     <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8"/>
-      <c r="D8" s="27" t="str" cm="1">
+      <c r="A8" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="25" t="str" cm="1">
         <f t="array" ref="D8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Australian Capital Territory</v>
       </c>
-      <c r="E8" s="27" t="str" cm="1">
+      <c r="E8" s="25" t="str" cm="1">
         <f t="array" ref="E8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>ACT</v>
       </c>
-      <c r="F8" s="27" t="str" cm="1">
+      <c r="F8" s="25" t="str" cm="1">
         <f t="array" ref="F8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>ACT</v>
       </c>
     </row>
     <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9"/>
-      <c r="D9" s="27" t="str" cm="1">
+      <c r="A9" s="12" t="str">
+        <f>HYPERLINK("#'Input - CO2 Use'!A1", "CO2 Use")</f>
+        <v>CO2 Use</v>
+      </c>
+      <c r="D9" s="25" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Victoria</v>
       </c>
-      <c r="E9" s="27" t="str" cm="1">
+      <c r="E9" s="25" t="str" cm="1">
         <f t="array" ref="E9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Victoria</v>
       </c>
-      <c r="F9" s="27" t="str" cm="1">
+      <c r="F9" s="25" t="str" cm="1">
         <f t="array" ref="F9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>VIC</v>
       </c>
     </row>
     <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
-      <c r="D10" s="27" t="str" cm="1">
+      <c r="D10" s="25" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Queensland</v>
       </c>
-      <c r="E10" s="27" t="str" cm="1">
+      <c r="E10" s="25" t="str" cm="1">
         <f t="array" ref="E10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Queensland</v>
       </c>
-      <c r="F10" s="27" t="str" cm="1">
+      <c r="F10" s="25" t="str" cm="1">
         <f t="array" ref="F10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>QLD</v>
       </c>
     </row>
     <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
-      <c r="D11" s="27" t="str" cm="1">
+      <c r="D11" s="25" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>South Australia</v>
       </c>
-      <c r="E11" s="27" t="str" cm="1">
+      <c r="E11" s="25" t="str" cm="1">
         <f t="array" ref="E11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>South Australia</v>
       </c>
-      <c r="F11" s="27" t="str" cm="1">
+      <c r="F11" s="25" t="str" cm="1">
         <f t="array" ref="F11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>SA</v>
       </c>
       <c r="BM11" s="2"/>
     </row>
     <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12"/>
-      <c r="D12" s="27" t="str" cm="1">
+      <c r="A12" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="25" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Western Australia</v>
       </c>
-      <c r="E12" s="27" t="str" cm="1">
+      <c r="E12" s="25" t="str" cm="1">
         <f t="array" ref="E12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Western Australia</v>
       </c>
-      <c r="F12" s="27" t="str" cm="1">
+      <c r="F12" s="25" t="str" cm="1">
         <f t="array" ref="F12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>WA</v>
       </c>
       <c r="BM12" s="2"/>
     </row>
     <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13"/>
-      <c r="D13" s="27" t="str" cm="1">
+      <c r="A13" s="12" t="str">
+        <f>HYPERLINK("#'12.1.1-2 Supplementary CO2'!A1", "12.1.1-2 Supplementary CO2")</f>
+        <v>12.1.1-2 Supplementary CO2</v>
+      </c>
+      <c r="D13" s="25" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Tasmania</v>
       </c>
-      <c r="E13" s="27" t="str" cm="1">
+      <c r="E13" s="25" t="str" cm="1">
         <f t="array" ref="E13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Tasmania</v>
       </c>
-      <c r="F13" s="27" t="str" cm="1">
+      <c r="F13" s="25" t="str" cm="1">
         <f t="array" ref="F13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>TAS</v>
       </c>
     </row>
     <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
-      <c r="D14" s="27" t="str" cm="1">
+      <c r="D14" s="25" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Northern Territory</v>
       </c>
-      <c r="E14" s="27" t="str" cm="1">
+      <c r="E14" s="25" t="str" cm="1">
         <f t="array" ref="E14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Northern Territory</v>
       </c>
-      <c r="F14" s="27" t="str" cm="1">
+      <c r="F14" s="25" t="str" cm="1">
         <f t="array" ref="F14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>NT</v>
       </c>
@@ -6701,10 +6696,15 @@
       <c r="A15"/>
     </row>
     <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16"/>
+      <c r="A16" s="65" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17"/>
+      <c r="A17" s="66" t="str">
+        <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
+        <v>Constants - Common</v>
+      </c>
     </row>
     <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
@@ -6722,76 +6722,76 @@
     </row>
     <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
-      <c r="D20" s="27" t="s">
-        <v>9</v>
+      <c r="D20" s="25" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
-      <c r="D21" s="27" t="str" cm="1">
+      <c r="D21" s="25" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
-      <c r="D22" s="27" t="str" cm="1">
+      <c r="D22" s="25" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Mandurah</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
-      <c r="D23" s="27" t="str" cm="1">
+      <c r="D23" s="25" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - Inner</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
-      <c r="D24" s="27" t="str" cm="1">
+      <c r="D24" s="25" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North East</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
-      <c r="D25" s="27" t="str" cm="1">
+      <c r="D25" s="25" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North West</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
-      <c r="D26" s="27" t="str" cm="1">
+      <c r="D26" s="25" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South East</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
-      <c r="D27" s="27" t="str" cm="1">
+      <c r="D27" s="25" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South West</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
-      <c r="D28" s="27" t="str" cm="1">
+      <c r="D28" s="25" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Wheat Belt</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
-      <c r="D29" s="27" t="str" cm="1">
+      <c r="D29" s="25" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (North)</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
-      <c r="D30" s="27" t="str" cm="1">
+      <c r="D30" s="25" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
@@ -6821,1342 +6821,1453 @@
     </row>
     <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
-      <c r="D36" s="27" t="s">
+      <c r="D36" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="25" t="s">
         <v>11</v>
-      </c>
-      <c r="E36" s="27" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
-      <c r="D37" s="27" t="str" cm="1">
+      <c r="D37" s="25" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>CO2</v>
       </c>
-      <c r="E37" s="27" cm="1">
+      <c r="E37" s="25" cm="1">
         <f t="array" ref="E37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
-      <c r="D38" s="27" t="str" cm="1">
+      <c r="D38" s="25" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>CH4</v>
       </c>
-      <c r="E38" s="27" cm="1">
+      <c r="E38" s="25" cm="1">
         <f t="array" ref="E38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
-      <c r="D39" s="27" t="str" cm="1">
+      <c r="D39" s="25" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>N2O</v>
       </c>
-      <c r="E39" s="27" cm="1">
+      <c r="E39" s="25" cm="1">
         <f t="array" ref="E39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>265</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
-      <c r="D40" s="27" t="str" cm="1">
+      <c r="D40" s="25" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>CF4</v>
       </c>
-      <c r="E40" s="27" cm="1">
+      <c r="E40" s="25" cm="1">
         <f t="array" ref="E40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>6630</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
-      <c r="D41" s="27" t="str" cm="1">
+      <c r="D41" s="25" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>C2F6</v>
       </c>
-      <c r="E41" s="27" cm="1">
+      <c r="E41" s="25" cm="1">
         <f t="array" ref="E41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>12200</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="27" t="str" cm="1">
+      <c r="A42"/>
+      <c r="D42" s="25" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>SF6</v>
       </c>
-      <c r="E42" s="27" cm="1">
+      <c r="E42" s="25" cm="1">
         <f t="array" ref="E42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>22800</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="27" t="str" cm="1">
+      <c r="A43"/>
+      <c r="D43" s="25" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>NF3</v>
       </c>
-      <c r="E43" s="27" cm="1">
+      <c r="E43" s="25" cm="1">
         <f t="array" ref="E43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>17200</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44"/>
+    </row>
     <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45"/>
       <c r="D45" s="5" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46"/>
       <c r="D46" s="4" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D47" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" s="27" t="s">
+      <c r="A47"/>
+      <c r="D47" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="F47" s="27" t="s">
+      <c r="G47" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="G47" s="27" t="s">
+      <c r="H47" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="H47" s="27" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D48" s="27" t="str" cm="1">
+      <c r="A48"/>
+      <c r="D48" s="25" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>CO2</v>
       </c>
-      <c r="E48" s="27" t="str" cm="1">
+      <c r="E48" s="25" t="str" cm="1">
         <f t="array" ref="E48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44/12</v>
       </c>
-      <c r="F48" s="27" cm="1">
+      <c r="F48" s="25" cm="1">
         <f t="array" ref="F48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44</v>
       </c>
-      <c r="G48" s="27" cm="1">
+      <c r="G48" s="25" cm="1">
         <f t="array" ref="G48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>12</v>
       </c>
-      <c r="H48" s="27">
+      <c r="H48" s="25">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="49" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D49" s="27" t="str" cm="1">
+    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49"/>
+      <c r="D49" s="25" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>CH4</v>
       </c>
-      <c r="E49" s="27" t="str" cm="1">
+      <c r="E49" s="25" t="str" cm="1">
         <f t="array" ref="E49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>16/12</v>
       </c>
-      <c r="F49" s="27" cm="1">
+      <c r="F49" s="25" cm="1">
         <f t="array" ref="F49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>16</v>
       </c>
-      <c r="G49" s="27" cm="1">
+      <c r="G49" s="25" cm="1">
         <f t="array" ref="G49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>12</v>
       </c>
-      <c r="H49" s="27">
+      <c r="H49" s="25">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="50" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D50" s="27" t="str" cm="1">
+    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50"/>
+      <c r="D50" s="25" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>N2O</v>
       </c>
-      <c r="E50" s="27" t="str" cm="1">
+      <c r="E50" s="25" t="str" cm="1">
         <f t="array" ref="E50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44/28</v>
       </c>
-      <c r="F50" s="27" cm="1">
+      <c r="F50" s="25" cm="1">
         <f t="array" ref="F50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44</v>
       </c>
-      <c r="G50" s="27" cm="1">
+      <c r="G50" s="25" cm="1">
         <f t="array" ref="G50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>28</v>
       </c>
-      <c r="H50" s="27">
+      <c r="H50" s="25">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>1.5714285714285714</v>
       </c>
     </row>
-    <row r="51" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D51" s="27" t="str" cm="1">
+    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51"/>
+      <c r="D51" s="25" t="str" cm="1">
         <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>Nox</v>
       </c>
-      <c r="E51" s="27" t="str" cm="1">
+      <c r="E51" s="25" t="str" cm="1">
         <f t="array" ref="E51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>46/14</v>
       </c>
-      <c r="F51" s="27" cm="1">
+      <c r="F51" s="25" cm="1">
         <f t="array" ref="F51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>46</v>
       </c>
-      <c r="G51" s="27" cm="1">
+      <c r="G51" s="25" cm="1">
         <f t="array" ref="G51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>14</v>
       </c>
-      <c r="H51" s="27">
+      <c r="H51" s="25">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>3.2857142857142856</v>
       </c>
     </row>
-    <row r="52" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D52" s="27" t="str" cm="1">
+    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52"/>
+      <c r="D52" s="25" t="str" cm="1">
         <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>CO</v>
       </c>
-      <c r="E52" s="27" t="str" cm="1">
+      <c r="E52" s="25" t="str" cm="1">
         <f t="array" ref="E52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>28/12</v>
       </c>
-      <c r="F52" s="27" cm="1">
+      <c r="F52" s="25" cm="1">
         <f t="array" ref="F52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>28</v>
       </c>
-      <c r="G52" s="27" cm="1">
+      <c r="G52" s="25" cm="1">
         <f t="array" ref="G52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>12</v>
       </c>
-      <c r="H52" s="27">
+      <c r="H52" s="25">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="53" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D53" s="27" t="str" cm="1">
+    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53"/>
+      <c r="D53" s="25" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>CO2 Lime</v>
       </c>
-      <c r="E53" s="27" t="str" cm="1">
+      <c r="E53" s="25" t="str" cm="1">
         <f t="array" ref="E53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44/12</v>
       </c>
-      <c r="F53" s="27" cm="1">
+      <c r="F53" s="25" cm="1">
         <f t="array" ref="F53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44</v>
       </c>
-      <c r="G53" s="27" cm="1">
+      <c r="G53" s="25" cm="1">
         <f t="array" ref="G53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>12</v>
       </c>
-      <c r="H53" s="27">
+      <c r="H53" s="25">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="54" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D54" s="27" t="str" cm="1">
+    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54"/>
+      <c r="D54" s="25" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>NMVOC</v>
       </c>
-      <c r="E54" s="27" t="str" cm="1">
+      <c r="E54" s="25" t="str" cm="1">
         <f t="array" ref="E54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>14/12</v>
       </c>
-      <c r="F54" s="27" cm="1">
+      <c r="F54" s="25" cm="1">
         <f t="array" ref="F54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>14</v>
       </c>
-      <c r="G54" s="27" cm="1">
+      <c r="G54" s="25" cm="1">
         <f t="array" ref="G54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>12</v>
       </c>
-      <c r="H54" s="27">
+      <c r="H54" s="25">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>1.1666666666666667</v>
       </c>
     </row>
-    <row r="55" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55"/>
+    </row>
+    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56"/>
+    </row>
+    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57"/>
       <c r="D57" s="5" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58"/>
       <c r="D58" s="4" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D59" s="30" t="str" cm="1">
+    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59"/>
+      <c r="D59" s="28" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D60" s="30" t="str">
+    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60"/>
+      <c r="D60" s="28" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D61" s="30" t="str">
+    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61"/>
+      <c r="D61" s="28" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D63" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="E63" s="27" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D64" s="27" t="str" cm="1">
+    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62"/>
+    </row>
+    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63"/>
+      <c r="D63" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="E63" s="25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64"/>
+      <c r="D64" s="25" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical montane</v>
       </c>
-      <c r="E64" s="27" t="str" cm="1">
+      <c r="E64" s="25" t="str" cm="1">
         <f t="array" ref="E64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="65" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D65" s="27" t="str" cm="1">
+    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65"/>
+      <c r="D65" s="25" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical wet</v>
       </c>
-      <c r="E65" s="27" t="str" cm="1">
+      <c r="E65" s="25" t="str" cm="1">
         <f t="array" ref="E65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="66" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D66" s="27" t="str" cm="1">
+    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66"/>
+      <c r="D66" s="25" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical moist</v>
       </c>
-      <c r="E66" s="27" t="str" cm="1">
+      <c r="E66" s="25" t="str" cm="1">
         <f t="array" ref="E66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="67" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D67" s="27" t="str" cm="1">
+    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67"/>
+      <c r="D67" s="25" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical dry</v>
       </c>
-      <c r="E67" s="27" t="str" cm="1">
+      <c r="E67" s="25" t="str" cm="1">
         <f t="array" ref="E67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="68" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D68" s="27" t="str" cm="1">
+    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68"/>
+      <c r="D68" s="25" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate moist</v>
       </c>
-      <c r="E68" s="27" t="str" cm="1">
+      <c r="E68" s="25" t="str" cm="1">
         <f t="array" ref="E68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="69" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D69" s="27" t="str" cm="1">
+    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69"/>
+      <c r="D69" s="25" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate dry</v>
       </c>
-      <c r="E69" s="27" t="str" cm="1">
+      <c r="E69" s="25" t="str" cm="1">
         <f t="array" ref="E69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="70" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D70" s="27" t="str" cm="1">
+    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70"/>
+      <c r="D70" s="25" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate moist</v>
       </c>
-      <c r="E70" s="27" t="str" cm="1">
+      <c r="E70" s="25" t="str" cm="1">
         <f t="array" ref="E70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="71" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D71" s="27" t="str" cm="1">
+    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71"/>
+      <c r="D71" s="25" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate dry</v>
       </c>
-      <c r="E71" s="27" t="str" cm="1">
+      <c r="E71" s="25" t="str" cm="1">
         <f t="array" ref="E71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="72" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D72" s="27" t="str" cm="1">
+    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72"/>
+      <c r="D72" s="25" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate moist - low frost</v>
       </c>
-      <c r="E72" s="27" t="str" cm="1">
+      <c r="E72" s="25" t="str" cm="1">
         <f t="array" ref="E72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="73" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D73" s="27" t="str" cm="1">
+    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73"/>
+      <c r="D73" s="25" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate dry - low frost</v>
       </c>
-      <c r="E73" s="27" t="str" cm="1">
+      <c r="E73" s="25" t="str" cm="1">
         <f t="array" ref="E73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="74" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D74" s="27" t="str" cm="1">
+    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74"/>
+      <c r="D74" s="25" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate moist - high temp</v>
       </c>
-      <c r="E74" s="27" t="str" cm="1">
+      <c r="E74" s="25" t="str" cm="1">
         <f t="array" ref="E74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="75" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D75" s="27" t="str" cm="1">
+    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75"/>
+      <c r="D75" s="25" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate dry - high temp</v>
       </c>
-      <c r="E75" s="27" t="str" cm="1">
+      <c r="E75" s="25" t="str" cm="1">
         <f t="array" ref="E75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="76" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D76" s="27" t="str" cm="1">
+    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76"/>
+      <c r="D76" s="25" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate moist - low frost</v>
       </c>
-      <c r="E76" s="27" t="str" cm="1">
+      <c r="E76" s="25" t="str" cm="1">
         <f t="array" ref="E76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="77" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D77" s="27" t="str" cm="1">
+    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77"/>
+      <c r="D77" s="25" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate dry - low frost</v>
       </c>
-      <c r="E77" s="27" t="str" cm="1">
+      <c r="E77" s="25" t="str" cm="1">
         <f t="array" ref="E77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="78" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78"/>
+    </row>
+    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79"/>
+    </row>
+    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80"/>
+    </row>
+    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81"/>
       <c r="D81" s="5" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82"/>
       <c r="D82" s="4" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D83" s="30" t="str" cm="1">
+    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83"/>
+      <c r="D83" s="28" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D84" s="30" t="str">
+    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84"/>
+      <c r="D84" s="28" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D85" s="30" t="str">
+    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85"/>
+      <c r="D85" s="28" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D86" s="30" t="str">
+    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86"/>
+      <c r="D86" s="28" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D87" s="30" t="str">
+    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87"/>
+      <c r="D87" s="28" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D89" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="E89" s="27" t="s">
+    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88"/>
+    </row>
+    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89"/>
+      <c r="D89" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F89" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="F89" s="27" t="s">
+      <c r="G89" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="G89" s="27" t="s">
+      <c r="H89" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="H89" s="27" t="s">
+      <c r="I89" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="I89" s="27" t="s">
+      <c r="J89" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="J89" s="27" t="s">
+      <c r="K89" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="K89" s="27" t="s">
+      <c r="L89" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="L89" s="27" t="s">
+      <c r="M89" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="M89" s="27" t="s">
+      <c r="N89" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="N89" s="27" t="s">
+      <c r="O89" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="P89" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="O89" s="27" t="s">
+      <c r="Q89" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="P89" s="27" t="s">
+      <c r="R89" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="Q89" s="27" t="s">
+      <c r="S89" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="R89" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="S89" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="T89" s="27"/>
-    </row>
-    <row r="90" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D90" s="27" t="str" cm="1">
+      <c r="T89" s="25"/>
+    </row>
+    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90"/>
+      <c r="D90" s="25" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical montane</v>
       </c>
-      <c r="E90" s="27" t="str" cm="1">
+      <c r="E90" s="25" t="str" cm="1">
         <f t="array" ref="E90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 18 C</v>
       </c>
-      <c r="F90" s="27" t="str" cm="1">
+      <c r="F90" s="25" t="str" cm="1">
         <f t="array" ref="F90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="G90" s="27" t="str" cm="1">
+      <c r="G90" s="25" t="str" cm="1">
         <f t="array" ref="G90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 7</v>
       </c>
-      <c r="H90" s="27" t="str" cm="1">
+      <c r="H90" s="25" t="str" cm="1">
         <f t="array" ref="H90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 1000 m</v>
       </c>
-      <c r="I90" s="27" t="str" cm="1">
+      <c r="I90" s="25" t="str" cm="1">
         <f t="array" ref="I90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="J90" s="27" cm="1">
+      <c r="J90" s="25" cm="1">
         <f t="array" ref="J90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>18.001000000000001</v>
       </c>
-      <c r="K90" s="27" cm="1">
+      <c r="K90" s="25" cm="1">
         <f t="array" ref="K90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L90" s="27" cm="1">
+      <c r="L90" s="25" cm="1">
         <f t="array" ref="L90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M90" s="27" cm="1">
+      <c r="M90" s="25" cm="1">
         <f t="array" ref="M90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N90" s="27" cm="1">
+      <c r="N90" s="25" cm="1">
         <f t="array" ref="N90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O90" s="27" cm="1">
+      <c r="O90" s="25" cm="1">
         <f t="array" ref="O90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>7</v>
       </c>
-      <c r="P90" s="27" cm="1">
+      <c r="P90" s="25" cm="1">
         <f t="array" ref="P90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1000</v>
       </c>
-      <c r="Q90" s="27" cm="1">
+      <c r="Q90" s="25" cm="1">
         <f t="array" ref="Q90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="R90" s="27" cm="1">
+      <c r="R90" s="25" cm="1">
         <f t="array" ref="R90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S90" s="27" cm="1">
+      <c r="S90" s="25" cm="1">
         <f t="array" ref="S90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T90" s="27"/>
-    </row>
-    <row r="91" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D91" s="27" t="str" cm="1">
+      <c r="T90" s="25"/>
+    </row>
+    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91"/>
+      <c r="D91" s="25" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical wet</v>
       </c>
-      <c r="E91" s="27" t="str" cm="1">
+      <c r="E91" s="25" t="str" cm="1">
         <f t="array" ref="E91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 18 C</v>
       </c>
-      <c r="F91" s="27" t="str" cm="1">
+      <c r="F91" s="25" t="str" cm="1">
         <f t="array" ref="F91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 2000 mm</v>
       </c>
-      <c r="G91" s="27" t="str" cm="1">
+      <c r="G91" s="25" t="str" cm="1">
         <f t="array" ref="G91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 7</v>
       </c>
-      <c r="H91" s="27" t="str" cm="1">
+      <c r="H91" s="25" t="str" cm="1">
         <f t="array" ref="H91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1000 m</v>
       </c>
-      <c r="I91" s="27" t="str" cm="1">
+      <c r="I91" s="25" t="str" cm="1">
         <f t="array" ref="I91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="J91" s="27" cm="1">
+      <c r="J91" s="25" cm="1">
         <f t="array" ref="J91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>18.001000000000001</v>
       </c>
-      <c r="K91" s="27" cm="1">
+      <c r="K91" s="25" cm="1">
         <f t="array" ref="K91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L91" s="27" cm="1">
+      <c r="L91" s="25" cm="1">
         <f t="array" ref="L91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>2000.001</v>
       </c>
-      <c r="M91" s="27" cm="1">
+      <c r="M91" s="25" cm="1">
         <f t="array" ref="M91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N91" s="27" cm="1">
+      <c r="N91" s="25" cm="1">
         <f t="array" ref="N91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O91" s="27" cm="1">
+      <c r="O91" s="25" cm="1">
         <f t="array" ref="O91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>7</v>
       </c>
-      <c r="P91" s="27" cm="1">
+      <c r="P91" s="25" cm="1">
         <f t="array" ref="P91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q91" s="27" cm="1">
+      <c r="Q91" s="25" cm="1">
         <f t="array" ref="Q91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999.99900000000002</v>
       </c>
-      <c r="R91" s="27" cm="1">
+      <c r="R91" s="25" cm="1">
         <f t="array" ref="R91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S91" s="27" cm="1">
+      <c r="S91" s="25" cm="1">
         <f t="array" ref="S91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T91" s="27"/>
-    </row>
-    <row r="92" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D92" s="27" t="str" cm="1">
+      <c r="T91" s="25"/>
+    </row>
+    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92"/>
+      <c r="D92" s="25" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical moist</v>
       </c>
-      <c r="E92" s="27" t="str" cm="1">
+      <c r="E92" s="25" t="str" cm="1">
         <f t="array" ref="E92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 18 C</v>
       </c>
-      <c r="F92" s="27" t="str" cm="1">
+      <c r="F92" s="25" t="str" cm="1">
         <f t="array" ref="F92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 1000 mm - ≤ 2000 mm</v>
       </c>
-      <c r="G92" s="27" t="str" cm="1">
+      <c r="G92" s="25" t="str" cm="1">
         <f t="array" ref="G92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 7</v>
       </c>
-      <c r="H92" s="27" t="str" cm="1">
+      <c r="H92" s="25" t="str" cm="1">
         <f t="array" ref="H92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1000 m</v>
       </c>
-      <c r="I92" s="27" t="str" cm="1">
+      <c r="I92" s="25" t="str" cm="1">
         <f t="array" ref="I92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="J92" s="27" cm="1">
+      <c r="J92" s="25" cm="1">
         <f t="array" ref="J92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>18.001000000000001</v>
       </c>
-      <c r="K92" s="27" cm="1">
+      <c r="K92" s="25" cm="1">
         <f t="array" ref="K92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L92" s="27" cm="1">
+      <c r="L92" s="25" cm="1">
         <f t="array" ref="L92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1000.001</v>
       </c>
-      <c r="M92" s="27" cm="1">
+      <c r="M92" s="25" cm="1">
         <f t="array" ref="M92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>2000</v>
       </c>
-      <c r="N92" s="27" cm="1">
+      <c r="N92" s="25" cm="1">
         <f t="array" ref="N92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O92" s="27" cm="1">
+      <c r="O92" s="25" cm="1">
         <f t="array" ref="O92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>7</v>
       </c>
-      <c r="P92" s="27" cm="1">
+      <c r="P92" s="25" cm="1">
         <f t="array" ref="P92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q92" s="27" cm="1">
+      <c r="Q92" s="25" cm="1">
         <f t="array" ref="Q92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999.99900000000002</v>
       </c>
-      <c r="R92" s="27" cm="1">
+      <c r="R92" s="25" cm="1">
         <f t="array" ref="R92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S92" s="27" cm="1">
+      <c r="S92" s="25" cm="1">
         <f t="array" ref="S92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T92" s="27"/>
-    </row>
-    <row r="93" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D93" s="27" t="str" cm="1">
+      <c r="T92" s="25"/>
+    </row>
+    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93"/>
+      <c r="D93" s="25" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical dry</v>
       </c>
-      <c r="E93" s="27" t="str" cm="1">
+      <c r="E93" s="25" t="str" cm="1">
         <f t="array" ref="E93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 18 C</v>
       </c>
-      <c r="F93" s="27" t="str" cm="1">
+      <c r="F93" s="25" t="str" cm="1">
         <f t="array" ref="F93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1000 mm</v>
       </c>
-      <c r="G93" s="27" t="str" cm="1">
+      <c r="G93" s="25" t="str" cm="1">
         <f t="array" ref="G93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 7</v>
       </c>
-      <c r="H93" s="27" t="str" cm="1">
+      <c r="H93" s="25" t="str" cm="1">
         <f t="array" ref="H93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1000 m</v>
       </c>
-      <c r="I93" s="27" t="str" cm="1">
+      <c r="I93" s="25" t="str" cm="1">
         <f t="array" ref="I93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="J93" s="27" cm="1">
+      <c r="J93" s="25" cm="1">
         <f t="array" ref="J93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>18.001000000000001</v>
       </c>
-      <c r="K93" s="27" cm="1">
+      <c r="K93" s="25" cm="1">
         <f t="array" ref="K93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L93" s="27" cm="1">
+      <c r="L93" s="25" cm="1">
         <f t="array" ref="L93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M93" s="27" cm="1">
+      <c r="M93" s="25" cm="1">
         <f t="array" ref="M93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1000</v>
       </c>
-      <c r="N93" s="27" cm="1">
+      <c r="N93" s="25" cm="1">
         <f t="array" ref="N93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O93" s="27" cm="1">
+      <c r="O93" s="25" cm="1">
         <f t="array" ref="O93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>7</v>
       </c>
-      <c r="P93" s="27" cm="1">
+      <c r="P93" s="25" cm="1">
         <f t="array" ref="P93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q93" s="27" cm="1">
+      <c r="Q93" s="25" cm="1">
         <f t="array" ref="Q93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999.99900000000002</v>
       </c>
-      <c r="R93" s="27" cm="1">
+      <c r="R93" s="25" cm="1">
         <f t="array" ref="R93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S93" s="27" cm="1">
+      <c r="S93" s="25" cm="1">
         <f t="array" ref="S93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T93" s="27"/>
-    </row>
-    <row r="94" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D94" s="27" t="str" cm="1">
+      <c r="T93" s="25"/>
+    </row>
+    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94"/>
+      <c r="D94" s="25" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate moist</v>
       </c>
-      <c r="E94" s="27" t="str" cm="1">
+      <c r="E94" s="25" t="str" cm="1">
         <f t="array" ref="E94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 10 C</v>
       </c>
-      <c r="F94" s="27" t="str" cm="1">
+      <c r="F94" s="25" t="str" cm="1">
         <f t="array" ref="F94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="G94" s="27" t="str" cm="1">
+      <c r="G94" s="25" t="str" cm="1">
         <f t="array" ref="G94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H94" s="27" t="str" cm="1">
+      <c r="H94" s="25" t="str" cm="1">
         <f t="array" ref="H94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="I94" s="27" t="str" cm="1">
+      <c r="I94" s="25" t="str" cm="1">
         <f t="array" ref="I94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 1</v>
       </c>
-      <c r="J94" s="27" cm="1">
+      <c r="J94" s="25" cm="1">
         <f t="array" ref="J94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>10.000999999999999</v>
       </c>
-      <c r="K94" s="27" cm="1">
+      <c r="K94" s="25" cm="1">
         <f t="array" ref="K94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L94" s="27" cm="1">
+      <c r="L94" s="25" cm="1">
         <f t="array" ref="L94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M94" s="27" cm="1">
+      <c r="M94" s="25" cm="1">
         <f t="array" ref="M94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N94" s="27" cm="1">
+      <c r="N94" s="25" cm="1">
         <f t="array" ref="N94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O94" s="27" cm="1">
+      <c r="O94" s="25" cm="1">
         <f t="array" ref="O94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="P94" s="27" cm="1">
+      <c r="P94" s="25" cm="1">
         <f t="array" ref="P94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q94" s="27" cm="1">
+      <c r="Q94" s="25" cm="1">
         <f t="array" ref="Q94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="R94" s="27" cm="1">
+      <c r="R94" s="25" cm="1">
         <f t="array" ref="R94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1.0009999999999999</v>
       </c>
-      <c r="S94" s="27" cm="1">
+      <c r="S94" s="25" cm="1">
         <f t="array" ref="S94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T94" s="27"/>
-    </row>
-    <row r="95" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D95" s="27" t="str" cm="1">
+      <c r="T94" s="25"/>
+    </row>
+    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95"/>
+      <c r="D95" s="25" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate dry</v>
       </c>
-      <c r="E95" s="27" t="str" cm="1">
+      <c r="E95" s="25" t="str" cm="1">
         <f t="array" ref="E95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 10 C</v>
       </c>
-      <c r="F95" s="27" t="str" cm="1">
+      <c r="F95" s="25" t="str" cm="1">
         <f t="array" ref="F95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="G95" s="27" t="str" cm="1">
+      <c r="G95" s="25" t="str" cm="1">
         <f t="array" ref="G95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H95" s="27" t="str" cm="1">
+      <c r="H95" s="25" t="str" cm="1">
         <f t="array" ref="H95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="I95" s="27" t="str" cm="1">
+      <c r="I95" s="25" t="str" cm="1">
         <f t="array" ref="I95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1</v>
       </c>
-      <c r="J95" s="27" cm="1">
+      <c r="J95" s="25" cm="1">
         <f t="array" ref="J95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>10.000999999999999</v>
       </c>
-      <c r="K95" s="27" cm="1">
+      <c r="K95" s="25" cm="1">
         <f t="array" ref="K95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L95" s="27" cm="1">
+      <c r="L95" s="25" cm="1">
         <f t="array" ref="L95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M95" s="27" cm="1">
+      <c r="M95" s="25" cm="1">
         <f t="array" ref="M95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N95" s="27" cm="1">
+      <c r="N95" s="25" cm="1">
         <f t="array" ref="N95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O95" s="27" cm="1">
+      <c r="O95" s="25" cm="1">
         <f t="array" ref="O95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="P95" s="27" cm="1">
+      <c r="P95" s="25" cm="1">
         <f t="array" ref="P95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q95" s="27" cm="1">
+      <c r="Q95" s="25" cm="1">
         <f t="array" ref="Q95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="R95" s="27" cm="1">
+      <c r="R95" s="25" cm="1">
         <f t="array" ref="R95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S95" s="27" cm="1">
+      <c r="S95" s="25" cm="1">
         <f t="array" ref="S95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1</v>
       </c>
-      <c r="T95" s="27"/>
-    </row>
-    <row r="96" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D96" s="27" t="str" cm="1">
+      <c r="T95" s="25"/>
+    </row>
+    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96"/>
+      <c r="D96" s="25" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate moist</v>
       </c>
-      <c r="E96" s="27" t="str" cm="1">
+      <c r="E96" s="25" t="str" cm="1">
         <f t="array" ref="E96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 0 C - ≤ 10 C</v>
       </c>
-      <c r="F96" s="27" t="str" cm="1">
+      <c r="F96" s="25" t="str" cm="1">
         <f t="array" ref="F96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="G96" s="27" t="str" cm="1">
+      <c r="G96" s="25" t="str" cm="1">
         <f t="array" ref="G96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H96" s="27" t="str" cm="1">
+      <c r="H96" s="25" t="str" cm="1">
         <f t="array" ref="H96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="I96" s="27" t="str" cm="1">
+      <c r="I96" s="25" t="str" cm="1">
         <f t="array" ref="I96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 1</v>
       </c>
-      <c r="J96" s="27" cm="1">
+      <c r="J96" s="25" cm="1">
         <f t="array" ref="J96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="K96" s="27" cm="1">
+      <c r="K96" s="25" cm="1">
         <f t="array" ref="K96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>10</v>
       </c>
-      <c r="L96" s="27" cm="1">
+      <c r="L96" s="25" cm="1">
         <f t="array" ref="L96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M96" s="27" cm="1">
+      <c r="M96" s="25" cm="1">
         <f t="array" ref="M96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N96" s="27" cm="1">
+      <c r="N96" s="25" cm="1">
         <f t="array" ref="N96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O96" s="27" cm="1">
+      <c r="O96" s="25" cm="1">
         <f t="array" ref="O96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="P96" s="27" cm="1">
+      <c r="P96" s="25" cm="1">
         <f t="array" ref="P96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q96" s="27" cm="1">
+      <c r="Q96" s="25" cm="1">
         <f t="array" ref="Q96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="R96" s="27" cm="1">
+      <c r="R96" s="25" cm="1">
         <f t="array" ref="R96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1.0009999999999999</v>
       </c>
-      <c r="S96" s="27" cm="1">
+      <c r="S96" s="25" cm="1">
         <f t="array" ref="S96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T96" s="27"/>
-    </row>
-    <row r="97" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D97" s="27" t="str" cm="1">
+      <c r="T96" s="25"/>
+    </row>
+    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97"/>
+      <c r="D97" s="25" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate dry</v>
       </c>
-      <c r="E97" s="27" t="str" cm="1">
+      <c r="E97" s="25" t="str" cm="1">
         <f t="array" ref="E97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 0 C - ≤ 10 C</v>
       </c>
-      <c r="F97" s="27" t="str" cm="1">
+      <c r="F97" s="25" t="str" cm="1">
         <f t="array" ref="F97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="G97" s="27" t="str" cm="1">
+      <c r="G97" s="25" t="str" cm="1">
         <f t="array" ref="G97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H97" s="27" t="str" cm="1">
+      <c r="H97" s="25" t="str" cm="1">
         <f t="array" ref="H97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="I97" s="27" t="str" cm="1">
+      <c r="I97" s="25" t="str" cm="1">
         <f t="array" ref="I97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1</v>
       </c>
-      <c r="J97" s="27" cm="1">
+      <c r="J97" s="25" cm="1">
         <f t="array" ref="J97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="K97" s="27" cm="1">
+      <c r="K97" s="25" cm="1">
         <f t="array" ref="K97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>10</v>
       </c>
-      <c r="L97" s="27" cm="1">
+      <c r="L97" s="25" cm="1">
         <f t="array" ref="L97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M97" s="27" cm="1">
+      <c r="M97" s="25" cm="1">
         <f t="array" ref="M97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N97" s="27" cm="1">
+      <c r="N97" s="25" cm="1">
         <f t="array" ref="N97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O97" s="27" cm="1">
+      <c r="O97" s="25" cm="1">
         <f t="array" ref="O97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="P97" s="27" cm="1">
+      <c r="P97" s="25" cm="1">
         <f t="array" ref="P97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q97" s="27" cm="1">
+      <c r="Q97" s="25" cm="1">
         <f t="array" ref="Q97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="R97" s="27" cm="1">
+      <c r="R97" s="25" cm="1">
         <f t="array" ref="R97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S97" s="27" cm="1">
+      <c r="S97" s="25" cm="1">
         <f t="array" ref="S97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1</v>
       </c>
-      <c r="T97" s="27"/>
-    </row>
-    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="29" t="str" cm="1">
+      <c r="T97" s="25"/>
+    </row>
+    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98"/>
+    </row>
+    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99"/>
+      <c r="D99" s="27" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D100" s="29" t="str">
+    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100"/>
+      <c r="D100" s="27" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D101" s="29" t="str">
+    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101"/>
+      <c r="D101" s="27" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D102" s="29" t="str">
+    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102"/>
+      <c r="D102" s="27" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D103" s="29"/>
-    </row>
-    <row r="104" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103"/>
+      <c r="D103" s="27"/>
+    </row>
+    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104"/>
+    </row>
+    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105"/>
       <c r="D105" s="5" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106"/>
       <c r="D106" s="4" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D107" s="30" t="str" cm="1">
+    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107"/>
+      <c r="D107" s="28" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D109" s="27" t="s">
+    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108"/>
+    </row>
+    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109"/>
+      <c r="D109" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="E109" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F109" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="E109" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="F109" s="27" t="s">
+      <c r="G109" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="G109" s="27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="110" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D110" s="27" t="str" cm="1">
+    </row>
+    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110"/>
+      <c r="D110" s="25" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>Warm</v>
       </c>
-      <c r="E110" s="27" t="str" cm="1">
+      <c r="E110" s="25" t="str" cm="1">
         <f t="array" ref="E110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>≥ 26 C</v>
       </c>
-      <c r="F110" s="27" cm="1">
+      <c r="F110" s="25" cm="1">
         <f t="array" ref="F110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>26</v>
       </c>
-      <c r="G110" s="27" cm="1">
+      <c r="G110" s="25" cm="1">
         <f t="array" ref="G110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D111" s="27" t="str" cm="1">
+    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111"/>
+      <c r="D111" s="25" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E111" s="27" t="str" cm="1">
+      <c r="E111" s="25" t="str" cm="1">
         <f t="array" ref="E111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>15 - 25 C</v>
       </c>
-      <c r="F111" s="27" cm="1">
+      <c r="F111" s="25" cm="1">
         <f t="array" ref="F111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>15</v>
       </c>
-      <c r="G111" s="27" cm="1">
+      <c r="G111" s="25" cm="1">
         <f t="array" ref="G111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>25.998999999999999</v>
       </c>
     </row>
-    <row r="112" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D112" s="27" t="str" cm="1">
+    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112"/>
+      <c r="D112" s="25" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E112" s="27" t="str" cm="1">
+      <c r="E112" s="25" t="str" cm="1">
         <f t="array" ref="E112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>≤ 14 C</v>
       </c>
-      <c r="F112" s="27" cm="1">
+      <c r="F112" s="25" cm="1">
         <f t="array" ref="F112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>-999999</v>
       </c>
-      <c r="G112" s="27" cm="1">
+      <c r="G112" s="25" cm="1">
         <f t="array" ref="G112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>14.999000000000001</v>
       </c>
     </row>
-    <row r="113" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113"/>
+    </row>
+    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114"/>
+    </row>
+    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115"/>
       <c r="D115" s="5" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
         <v>VEERG Australian rainfall zones</v>
       </c>
       <c r="BN115" s="6"/>
     </row>
-    <row r="116" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116"/>
       <c r="D116" s="4" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
       <c r="BN116" s="6"/>
     </row>
-    <row r="117" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D117" s="30" t="str" cm="1">
+    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117"/>
+      <c r="D117" s="28" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra Rainfall min and Rainfall max columns to calculate zone from real rainfall data.</v>
       </c>
       <c r="BN117" s="6"/>
     </row>
-    <row r="118" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118"/>
       <c r="BN118" s="6"/>
     </row>
-    <row r="119" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D119" s="27" t="s">
+    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119"/>
+      <c r="D119" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="E119" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="E119" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="F119" s="27" t="s">
+      <c r="F119" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G119" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="G119" s="27" t="s">
-        <v>27</v>
-      </c>
       <c r="BN119" s="6"/>
     </row>
-    <row r="120" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D120" s="27" t="str" cm="1">
+    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120"/>
+      <c r="D120" s="25" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>High rainfall</v>
       </c>
-      <c r="E120" s="27" t="str" cm="1">
+      <c r="E120" s="25" t="str" cm="1">
         <f t="array" ref="E120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>Annual rainfall &gt; 600mm</v>
       </c>
-      <c r="F120" s="27" cm="1">
+      <c r="F120" s="25" cm="1">
         <f t="array" ref="F120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>600.00099999999998</v>
       </c>
-      <c r="G120" s="27" cm="1">
+      <c r="G120" s="25" cm="1">
         <f t="array" ref="G120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>999999</v>
       </c>
       <c r="BN120" s="6"/>
     </row>
-    <row r="121" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D121" s="27" t="str" cm="1">
+    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121"/>
+      <c r="D121" s="25" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>Low rainfall</v>
       </c>
-      <c r="E121" s="27" t="str" cm="1">
+      <c r="E121" s="25" t="str" cm="1">
         <f t="array" ref="E121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>Annual rainfall ≤ 600mm</v>
       </c>
-      <c r="F121" s="27" cm="1">
+      <c r="F121" s="25" cm="1">
         <f t="array" ref="F121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>-999999</v>
       </c>
-      <c r="G121" s="27" cm="1">
+      <c r="G121" s="25" cm="1">
         <f t="array" ref="G121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>600</v>
       </c>
       <c r="BN121" s="6"/>
     </row>
-    <row r="122" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122"/>
       <c r="BN122" s="6"/>
     </row>
-    <row r="123" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123"/>
+    </row>
+    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124"/>
       <c r="D124" s="5" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125"/>
       <c r="D125" s="4" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D127" s="27" t="s">
+    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126"/>
+    </row>
+    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127"/>
+      <c r="D127" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="E127" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="E127" s="27" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="128" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D128" s="27" t="str" cm="1">
+    </row>
+    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128"/>
+      <c r="D128" s="25" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
         <v>Leaching occurs</v>
       </c>
-      <c r="E128" s="27" t="str" cm="1">
+      <c r="E128" s="25" t="str" cm="1">
         <f t="array" ref="E128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="129" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D129" s="27" t="str" cm="1">
+    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129"/>
+      <c r="D129" s="25" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
         <v>Leaching does not occur</v>
       </c>
-      <c r="E129" s="27" t="str" cm="1">
+      <c r="E129" s="25" t="str" cm="1">
         <f t="array" ref="E129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="130" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130"/>
+    </row>
+    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131"/>
+    </row>
+    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132"/>
       <c r="D132" s="5" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
-      <c r="E132" s="18"/>
-    </row>
-    <row r="133" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E132" s="16"/>
+    </row>
+    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133"/>
       <c r="D133" s="4" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
-      <c r="E133" s="18"/>
-    </row>
-    <row r="134" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E133" s="16"/>
+    </row>
+    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134"/>
       <c r="D134" t="s">
+        <v>46</v>
+      </c>
+      <c r="E134" t="s">
         <v>47</v>
       </c>
-      <c r="E134" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="135" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135"/>
       <c r="D135" t="str" cm="1">
         <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
         <v>Yes - in leaching zone</v>
@@ -8166,18 +8277,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136"/>
       <c r="D136" s="1" t="str" cm="1">
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
         <v>No - not in leaching zone</v>
       </c>
-      <c r="E136" s="27" cm="1">
+      <c r="E136" s="25" cm="1">
         <f t="array" ref="E136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137"/>
+    </row>
+    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138"/>
       <c r="BN138" s="6"/>
       <c r="BO138" s="6"/>
       <c r="BP138" s="6"/>
@@ -8191,7 +8306,8 @@
       <c r="BX138" s="6"/>
       <c r="BY138" s="6"/>
     </row>
-    <row r="139" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139"/>
       <c r="D139" s="5" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
         <v>FracWET for irrigation types</v>
@@ -8209,7 +8325,8 @@
       <c r="BX139" s="6"/>
       <c r="BY139" s="6"/>
     </row>
-    <row r="140" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140"/>
       <c r="D140" s="4" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
         <v>VEERG 2026: Chapter 1, section 1.8.2 Leaching, climate and rainfall zones</v>
@@ -8227,106 +8344,119 @@
       <c r="BX140" s="6"/>
       <c r="BY140" s="6"/>
     </row>
-    <row r="141" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D141" s="30" t="str" cm="1">
+    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141"/>
+      <c r="D141" s="28" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Table created based on VEERG text 'Areas are subject to leaching (i.e., in the leaching zone) when... the land is irrigated (except drip irrigation).'</v>
       </c>
       <c r="BN141" s="6"/>
     </row>
-    <row r="142" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D142" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="E142" s="27" t="s">
-        <v>48</v>
+    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142"/>
+      <c r="D142" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="E142" s="25" t="s">
+        <v>47</v>
       </c>
       <c r="BN142" s="6"/>
     </row>
-    <row r="143" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D143" s="27" t="str" cm="1">
+    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143"/>
+      <c r="D143" s="25" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Not irrigated</v>
       </c>
-      <c r="E143" s="27" cm="1">
+      <c r="E143" s="25" cm="1">
         <f t="array" ref="E143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>0</v>
       </c>
       <c r="BN143" s="6"/>
     </row>
-    <row r="144" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144"/>
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Drip irrigation</v>
       </c>
-      <c r="E144" s="27" cm="1">
+      <c r="E144" s="25" cm="1">
         <f t="array" ref="E144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>0</v>
       </c>
       <c r="BN144" s="6"/>
     </row>
-    <row r="145" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145"/>
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Sprinkler irrigation</v>
       </c>
-      <c r="E145" s="27" cm="1">
+      <c r="E145" s="25" cm="1">
         <f t="array" ref="E145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>1</v>
       </c>
       <c r="BN145" s="6"/>
     </row>
-    <row r="146" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146"/>
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Surface irrigation</v>
       </c>
-      <c r="E146" s="27" cm="1">
+      <c r="E146" s="25" cm="1">
         <f t="array" ref="E146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>1</v>
       </c>
       <c r="BN146" s="6"/>
     </row>
-    <row r="147" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147"/>
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Other irrigation</v>
       </c>
-      <c r="E147" s="27" cm="1">
+      <c r="E147" s="25" cm="1">
         <f t="array" ref="E147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>1</v>
       </c>
       <c r="BN147" s="6"/>
     </row>
-    <row r="148" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148"/>
       <c r="BN148" s="6"/>
     </row>
-    <row r="149" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149"/>
       <c r="BN149" s="6"/>
     </row>
-    <row r="150" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150"/>
       <c r="D150" s="5" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
         <v>Australian data scores for scope 3</v>
       </c>
       <c r="BN150" s="6"/>
     </row>
-    <row r="151" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151"/>
       <c r="D151" s="4" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
         <v>VEERG 2026: XXXXXXXX</v>
       </c>
       <c r="BN151" s="6"/>
     </row>
-    <row r="152" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152"/>
       <c r="BN152" s="6"/>
     </row>
-    <row r="153" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D153" s="27" t="s">
+    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153"/>
+      <c r="D153" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="E153" s="25" t="s">
         <v>43</v>
-      </c>
-      <c r="E153" s="27" t="s">
-        <v>44</v>
       </c>
       <c r="BC153" s="2"/>
       <c r="BD153" s="2"/>
@@ -8340,12 +8470,13 @@
       <c r="BL153" s="2"/>
       <c r="BM153" s="2"/>
     </row>
-    <row r="154" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D154" s="27" t="str" cm="1">
+    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154"/>
+      <c r="D154" s="25" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>International scope 3 database</v>
       </c>
-      <c r="E154" s="27" cm="1">
+      <c r="E154" s="25" cm="1">
         <f t="array" ref="E154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>1</v>
       </c>
@@ -8361,12 +8492,13 @@
       <c r="BL154" s="2"/>
       <c r="BM154" s="2"/>
     </row>
-    <row r="155" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D155" s="27" t="str" cm="1">
+    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155"/>
+      <c r="D155" s="25" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>Australian scope 3 database</v>
       </c>
-      <c r="E155" s="27" cm="1">
+      <c r="E155" s="25" cm="1">
         <f t="array" ref="E155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>2</v>
       </c>
@@ -8382,65 +8514,72 @@
       <c r="BL155" s="2"/>
       <c r="BM155" s="2"/>
     </row>
-    <row r="156" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D156" s="27" t="str" cm="1">
+    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156"/>
+      <c r="D156" s="25" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>State or regional scope 3 database</v>
       </c>
-      <c r="E156" s="27" cm="1">
+      <c r="E156" s="25" cm="1">
         <f t="array" ref="E156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D157" s="27" t="str" cm="1">
+    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157"/>
+      <c r="D157" s="25" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>Emissions intensity calculated from approved method</v>
       </c>
-      <c r="E157" s="27" cm="1">
+      <c r="E157" s="25" cm="1">
         <f t="array" ref="E157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D158" s="27" t="str" cm="1">
+    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158"/>
+      <c r="D158" s="25" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>Verified credential matching ISO14067</v>
       </c>
-      <c r="E158" s="27" cm="1">
+      <c r="E158" s="25" cm="1">
         <f t="array" ref="E158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159"/>
+    </row>
+    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160"/>
+    </row>
     <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="5" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
-      <c r="E161" s="18"/>
+      <c r="E161" s="16"/>
     </row>
     <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="4" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
-      <c r="E162" s="18"/>
+      <c r="E162" s="16"/>
     </row>
     <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="4" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
-      <c r="E163" s="18"/>
+      <c r="E163" s="16"/>
     </row>
     <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D164" s="18" t="str" cm="1">
+      <c r="D164" s="16" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
       </c>
-      <c r="E164" s="18">
+      <c r="E164" s="16">
         <v>0.24</v>
       </c>
     </row>
@@ -8526,7 +8665,7 @@
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
       </c>
-      <c r="E175" s="29" t="str" cm="1">
+      <c r="E175" s="27" t="str" cm="1">
         <f t="array" ref="E175">Common_SourceData.Common_SourceData_DensityOfMethane_Unit()</f>
         <v>kg/m3</v>
       </c>
@@ -8563,336 +8702,336 @@
       <c r="BP179" s="6"/>
     </row>
     <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D180" s="29" t="str" cm="1">
+      <c r="D180" s="27" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
     <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D181" s="30" t="str" cm="1">
+      <c r="D181" s="28" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
     <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D182" s="30" t="str">
+      <c r="D182" s="28" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
     <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D183" s="30" t="str">
+      <c r="D183" s="28" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
     <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D184" s="30" t="str">
+      <c r="D184" s="28" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
     <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D185" s="30" t="str">
+      <c r="D185" s="28" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
     <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D186" s="27" t="s">
+      <c r="D186" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="E186" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E186" s="27" t="s">
+      <c r="F186" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="F186" s="27" t="s">
+      <c r="G186" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="G186" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="H186" s="27" t="s">
-        <v>18</v>
+      <c r="H186" s="25" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D187" s="27" t="str" cm="1">
+      <c r="D187" s="25" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
       </c>
-      <c r="E187" s="27" cm="1">
+      <c r="E187" s="25" cm="1">
         <f t="array" ref="E187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>5.8999999999999999E-3</v>
       </c>
-      <c r="F187" s="27" t="str" cm="1">
+      <c r="F187" s="25" t="str" cm="1">
         <f t="array" ref="F187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Pasture</v>
       </c>
-      <c r="G187" s="27" t="str" cm="1">
+      <c r="G187" s="25" t="str" cm="1">
         <f t="array" ref="G187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H187" s="27" t="str" cm="1">
+      <c r="H187" s="25" t="str" cm="1">
         <f t="array" ref="H187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D188" s="27" t="str" cm="1">
+      <c r="D188" s="25" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
       </c>
-      <c r="E188" s="27" cm="1">
+      <c r="E188" s="25" cm="1">
         <f t="array" ref="E188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="F188" s="27" t="str" cm="1">
+      <c r="F188" s="25" t="str" cm="1">
         <f t="array" ref="F188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Crop</v>
       </c>
-      <c r="G188" s="27" t="str" cm="1">
+      <c r="G188" s="25" t="str" cm="1">
         <f t="array" ref="G188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H188" s="27" t="str" cm="1">
+      <c r="H188" s="25" t="str" cm="1">
         <f t="array" ref="H188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D189" s="27" t="str" cm="1">
+      <c r="D189" s="25" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
       </c>
-      <c r="E189" s="27" cm="1">
+      <c r="E189" s="25" cm="1">
         <f t="array" ref="E189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>1.8E-3</v>
       </c>
-      <c r="F189" s="27" t="str" cm="1">
+      <c r="F189" s="25" t="str" cm="1">
         <f t="array" ref="F189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Pasture</v>
       </c>
-      <c r="G189" s="27" t="str" cm="1">
+      <c r="G189" s="25" t="str" cm="1">
         <f t="array" ref="G189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Not irrigated</v>
       </c>
-      <c r="H189" s="27" t="str" cm="1">
+      <c r="H189" s="25" t="str" cm="1">
         <f t="array" ref="H189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Low rainfall</v>
       </c>
     </row>
     <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D190" s="27" t="str" cm="1">
+      <c r="D190" s="25" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
       </c>
-      <c r="E190" s="27" cm="1">
+      <c r="E190" s="25" cm="1">
         <f t="array" ref="E190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>1.8E-3</v>
       </c>
-      <c r="F190" s="27" t="str" cm="1">
+      <c r="F190" s="25" t="str" cm="1">
         <f t="array" ref="F190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Pasture</v>
       </c>
-      <c r="G190" s="27" t="str" cm="1">
+      <c r="G190" s="25" t="str" cm="1">
         <f t="array" ref="G190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Not irrigated</v>
       </c>
-      <c r="H190" s="27" t="str" cm="1">
+      <c r="H190" s="25" t="str" cm="1">
         <f t="array" ref="H190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>High rainfall</v>
       </c>
     </row>
     <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D191" s="27" t="str" cm="1">
+      <c r="D191" s="25" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
       </c>
-      <c r="E191" s="27" cm="1">
+      <c r="E191" s="25" cm="1">
         <f t="array" ref="E191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="F191" s="27" t="str" cm="1">
+      <c r="F191" s="25" t="str" cm="1">
         <f t="array" ref="F191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Crop</v>
       </c>
-      <c r="G191" s="27" t="str" cm="1">
+      <c r="G191" s="25" t="str" cm="1">
         <f t="array" ref="G191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Not irrigated</v>
       </c>
-      <c r="H191" s="27" t="str" cm="1">
+      <c r="H191" s="25" t="str" cm="1">
         <f t="array" ref="H191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Low rainfall</v>
       </c>
     </row>
     <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D192" s="27" t="str" cm="1">
+      <c r="D192" s="25" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
       </c>
-      <c r="E192" s="27" cm="1">
+      <c r="E192" s="25" cm="1">
         <f t="array" ref="E192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="F192" s="27" t="str" cm="1">
+      <c r="F192" s="25" t="str" cm="1">
         <f t="array" ref="F192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Crop</v>
       </c>
-      <c r="G192" s="27" t="str" cm="1">
+      <c r="G192" s="25" t="str" cm="1">
         <f t="array" ref="G192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Not irrigated</v>
       </c>
-      <c r="H192" s="27" t="str" cm="1">
+      <c r="H192" s="25" t="str" cm="1">
         <f t="array" ref="H192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>High rainfall</v>
       </c>
     </row>
     <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D193" s="27" t="str" cm="1">
+      <c r="D193" s="25" t="str" cm="1">
         <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
       </c>
-      <c r="E193" s="27" cm="1">
+      <c r="E193" s="25" cm="1">
         <f t="array" ref="E193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>1.9900000000000001E-2</v>
       </c>
-      <c r="F193" s="27" t="str" cm="1">
+      <c r="F193" s="25" t="str" cm="1">
         <f t="array" ref="F193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
       </c>
-      <c r="G193" s="27" t="str" cm="1">
+      <c r="G193" s="25" t="str" cm="1">
         <f t="array" ref="G193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H193" s="27" t="str" cm="1">
+      <c r="H193" s="25" t="str" cm="1">
         <f t="array" ref="H193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D194" s="27" t="str" cm="1">
+      <c r="D194" s="25" t="str" cm="1">
         <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
       </c>
-      <c r="E194" s="27" cm="1">
+      <c r="E194" s="25" cm="1">
         <f t="array" ref="E194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>5.3E-3</v>
       </c>
-      <c r="F194" s="27" t="str" cm="1">
+      <c r="F194" s="25" t="str" cm="1">
         <f t="array" ref="F194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
       </c>
-      <c r="G194" s="27" t="str" cm="1">
+      <c r="G194" s="25" t="str" cm="1">
         <f t="array" ref="G194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H194" s="27" t="str" cm="1">
+      <c r="H194" s="25" t="str" cm="1">
         <f t="array" ref="H194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D195" s="27" t="str" cm="1">
+      <c r="D195" s="25" t="str" cm="1">
         <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
       </c>
-      <c r="E195" s="27" cm="1">
+      <c r="E195" s="25" cm="1">
         <f t="array" ref="E195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="F195" s="27" t="str" cm="1">
+      <c r="F195" s="25" t="str" cm="1">
         <f t="array" ref="F195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
       </c>
-      <c r="G195" s="27" t="str" cm="1">
+      <c r="G195" s="25" t="str" cm="1">
         <f t="array" ref="G195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H195" s="27" t="str" cm="1">
+      <c r="H195" s="25" t="str" cm="1">
         <f t="array" ref="H195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D196" s="27" t="str" cm="1">
+      <c r="D196" s="25" t="str" cm="1">
         <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (continuous flooding)</v>
       </c>
-      <c r="E196" s="27" cm="1">
+      <c r="E196" s="25" cm="1">
         <f t="array" ref="E196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F196" s="27" t="str" cm="1">
+      <c r="F196" s="25" t="str" cm="1">
         <f t="array" ref="F196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice</v>
       </c>
-      <c r="G196" s="27" t="str" cm="1">
+      <c r="G196" s="25" t="str" cm="1">
         <f t="array" ref="G196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Continuous flooding</v>
       </c>
-      <c r="H196" s="27" t="str" cm="1">
+      <c r="H196" s="25" t="str" cm="1">
         <f t="array" ref="H196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="197" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D197" s="27" t="str" cm="1">
+      <c r="D197" s="25" t="str" cm="1">
         <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
       </c>
-      <c r="E197" s="27" cm="1">
+      <c r="E197" s="25" cm="1">
         <f t="array" ref="E197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F197" s="27" t="str" cm="1">
+      <c r="F197" s="25" t="str" cm="1">
         <f t="array" ref="F197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice</v>
       </c>
-      <c r="G197" s="27" t="str" cm="1">
+      <c r="G197" s="25" t="str" cm="1">
         <f t="array" ref="G197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Single and multiple drainage, or alternate wetting and drying</v>
       </c>
-      <c r="H197" s="27" t="str" cm="1">
+      <c r="H197" s="25" t="str" cm="1">
         <f t="array" ref="H197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="198" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D198" s="27" t="str" cm="1">
+      <c r="D198" s="25" t="str" cm="1">
         <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
       </c>
-      <c r="E198" s="27" cm="1">
+      <c r="E198" s="25" cm="1">
         <f t="array" ref="E198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="F198" s="27" t="str" cm="1">
+      <c r="F198" s="25" t="str" cm="1">
         <f t="array" ref="F198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
       </c>
-      <c r="G198" s="27" t="str" cm="1">
+      <c r="G198" s="25" t="str" cm="1">
         <f t="array" ref="G198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H198" s="27" t="str" cm="1">
+      <c r="H198" s="25" t="str" cm="1">
         <f t="array" ref="H198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="199" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D199" s="27" t="str" cm="1">
+      <c r="D199" s="25" t="str" cm="1">
         <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
       </c>
-      <c r="E199" s="27" cm="1">
+      <c r="E199" s="25" cm="1">
         <f t="array" ref="E199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>1.8E-3</v>
       </c>
-      <c r="F199" s="27" t="str" cm="1">
+      <c r="F199" s="25" t="str" cm="1">
         <f t="array" ref="F199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
       </c>
-      <c r="G199" s="27" t="str" cm="1">
+      <c r="G199" s="25" t="str" cm="1">
         <f t="array" ref="G199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H199" s="27" t="str" cm="1">
+      <c r="H199" s="25" t="str" cm="1">
         <f t="array" ref="H199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
@@ -8910,31 +9049,31 @@
       </c>
     </row>
     <row r="204" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D204" s="30" t="str" cm="1">
+      <c r="D204" s="28" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
     </row>
     <row r="205" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D205" s="29" t="str" cm="1">
+      <c r="D205" s="27" t="str" cm="1">
         <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
     <row r="206" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D206" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="E206" s="27" t="s">
-        <v>59</v>
+      <c r="D206" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="E206" s="25" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="207" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D207" s="27" t="str" cm="1">
+      <c r="D207" s="25" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
-      <c r="E207" s="27" cm="1">
+      <c r="E207" s="25" cm="1">
         <f t="array" ref="E207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>6.0000000000000001E-3</v>
       </c>
@@ -8944,7 +9083,7 @@
         <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
-      <c r="E208" s="27" cm="1">
+      <c r="E208" s="25" cm="1">
         <f t="array" ref="E208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>2E-3</v>
       </c>
@@ -8956,19 +9095,19 @@
       </c>
     </row>
     <row r="212" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D212" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="E212" s="27" t="s">
-        <v>62</v>
+      <c r="D212" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="E212" s="25" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="213" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D213" s="27" t="str" cm="1">
+      <c r="D213" s="25" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
       </c>
-      <c r="E213" s="27" t="str" cm="1">
+      <c r="E213" s="25" t="str" cm="1">
         <f t="array" ref="E213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Summer</v>
       </c>
@@ -8978,7 +9117,7 @@
         <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>February</v>
       </c>
-      <c r="E214" s="27" t="str" cm="1">
+      <c r="E214" s="25" t="str" cm="1">
         <f t="array" ref="E214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Summer</v>
       </c>
@@ -8988,7 +9127,7 @@
         <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>March</v>
       </c>
-      <c r="E215" s="27" t="str" cm="1">
+      <c r="E215" s="25" t="str" cm="1">
         <f t="array" ref="E215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Autumn</v>
       </c>
@@ -8998,7 +9137,7 @@
         <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>April</v>
       </c>
-      <c r="E216" s="27" t="str" cm="1">
+      <c r="E216" s="25" t="str" cm="1">
         <f t="array" ref="E216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Autumn</v>
       </c>
@@ -9008,7 +9147,7 @@
         <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>May</v>
       </c>
-      <c r="E217" s="27" t="str" cm="1">
+      <c r="E217" s="25" t="str" cm="1">
         <f t="array" ref="E217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Autumn</v>
       </c>
@@ -9018,7 +9157,7 @@
         <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>June</v>
       </c>
-      <c r="E218" s="27" t="str" cm="1">
+      <c r="E218" s="25" t="str" cm="1">
         <f t="array" ref="E218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Winter</v>
       </c>
@@ -9028,7 +9167,7 @@
         <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>July</v>
       </c>
-      <c r="E219" s="27" t="str" cm="1">
+      <c r="E219" s="25" t="str" cm="1">
         <f t="array" ref="E219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Winter</v>
       </c>
@@ -9038,7 +9177,7 @@
         <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>August</v>
       </c>
-      <c r="E220" s="27" t="str" cm="1">
+      <c r="E220" s="25" t="str" cm="1">
         <f t="array" ref="E220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Winter</v>
       </c>
@@ -9048,7 +9187,7 @@
         <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>September</v>
       </c>
-      <c r="E221" s="27" t="str" cm="1">
+      <c r="E221" s="25" t="str" cm="1">
         <f t="array" ref="E221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Spring</v>
       </c>
@@ -9058,7 +9197,7 @@
         <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>October</v>
       </c>
-      <c r="E222" s="27" t="str" cm="1">
+      <c r="E222" s="25" t="str" cm="1">
         <f t="array" ref="E222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Spring</v>
       </c>
@@ -9068,7 +9207,7 @@
         <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>November</v>
       </c>
-      <c r="E223" s="27" t="str" cm="1">
+      <c r="E223" s="25" t="str" cm="1">
         <f t="array" ref="E223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Spring</v>
       </c>
@@ -9078,7 +9217,7 @@
         <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>December</v>
       </c>
-      <c r="E224" s="27" t="str" cm="1">
+      <c r="E224" s="25" t="str" cm="1">
         <f t="array" ref="E224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Summer</v>
       </c>
@@ -9096,123 +9235,123 @@
       </c>
     </row>
     <row r="229" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D229" s="30" t="str" cm="1">
+      <c r="D229" s="28" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
     <row r="231" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D231" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E231" s="27" t="s">
+      <c r="D231" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E231" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="F231" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="F231" s="26" t="s">
+      <c r="G231" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="H231" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="G231" s="27" t="s">
+      <c r="I231" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="J231" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="K231" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="L231" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="M231" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="N231" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="O231" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="P231" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q231" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="R231" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H231" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="I231" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="J231" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="K231" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="L231" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="M231" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="N231" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="O231" s="27" t="s">
+      <c r="S231" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="P231" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q231" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="R231" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="S231" s="27" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="232" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D232" s="27" t="str" cm="1">
+      <c r="D232" s="25" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E232" s="27" t="str" cm="1">
+      <c r="E232" s="25" t="str" cm="1">
         <f t="array" ref="E232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>≤10</v>
       </c>
-      <c r="F232" s="27" cm="1">
+      <c r="F232" s="25" cm="1">
         <f t="array" ref="F232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.66</v>
       </c>
-      <c r="G232" s="27" cm="1">
+      <c r="G232" s="25" cm="1">
         <f t="array" ref="G232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H232" s="27" cm="1">
+      <c r="H232" s="25" cm="1">
         <f t="array" ref="H232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="I232" s="27" cm="1">
+      <c r="I232" s="25" cm="1">
         <f t="array" ref="I232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1E-3</v>
       </c>
-      <c r="J232" s="27" cm="1">
+      <c r="J232" s="25" cm="1">
         <f t="array" ref="J232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K232" s="27" cm="1">
+      <c r="K232" s="25" cm="1">
         <f t="array" ref="K232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L232" s="27" cm="1">
+      <c r="L232" s="25" cm="1">
         <f t="array" ref="L232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M232" s="27" cm="1">
+      <c r="M232" s="25" cm="1">
         <f t="array" ref="M232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N232" s="27" cm="1">
+      <c r="N232" s="25" cm="1">
         <f t="array" ref="N232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O232" s="27" cm="1">
+      <c r="O232" s="25" cm="1">
         <f t="array" ref="O232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P232" s="27" cm="1">
+      <c r="P232" s="25" cm="1">
         <f t="array" ref="P232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q232" s="27" cm="1">
+      <c r="Q232" s="25" cm="1">
         <f t="array" ref="Q232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R232" s="27" cm="1">
+      <c r="R232" s="25" cm="1">
         <f t="array" ref="R232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S232" s="27" cm="1">
+      <c r="S232" s="25" cm="1">
         <f t="array" ref="S232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>10</v>
       </c>
@@ -9222,63 +9361,63 @@
         <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E233" s="27" cm="1">
+      <c r="E233" s="25" cm="1">
         <f t="array" ref="E233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>11</v>
       </c>
-      <c r="F233" s="27" cm="1">
+      <c r="F233" s="25" cm="1">
         <f t="array" ref="F233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.68</v>
       </c>
-      <c r="G233" s="27" cm="1">
+      <c r="G233" s="25" cm="1">
         <f t="array" ref="G233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H233" s="27" cm="1">
+      <c r="H233" s="25" cm="1">
         <f t="array" ref="H233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.11</v>
       </c>
-      <c r="I233" s="27" cm="1">
+      <c r="I233" s="25" cm="1">
         <f t="array" ref="I233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1E-3</v>
       </c>
-      <c r="J233" s="27" cm="1">
+      <c r="J233" s="25" cm="1">
         <f t="array" ref="J233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K233" s="27" cm="1">
+      <c r="K233" s="25" cm="1">
         <f t="array" ref="K233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L233" s="27" cm="1">
+      <c r="L233" s="25" cm="1">
         <f t="array" ref="L233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M233" s="27" cm="1">
+      <c r="M233" s="25" cm="1">
         <f t="array" ref="M233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N233" s="27" cm="1">
+      <c r="N233" s="25" cm="1">
         <f t="array" ref="N233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O233" s="27" cm="1">
+      <c r="O233" s="25" cm="1">
         <f t="array" ref="O233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P233" s="27" cm="1">
+      <c r="P233" s="25" cm="1">
         <f t="array" ref="P233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q233" s="27" cm="1">
+      <c r="Q233" s="25" cm="1">
         <f t="array" ref="Q233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R233" s="27" cm="1">
+      <c r="R233" s="25" cm="1">
         <f t="array" ref="R233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S233" s="27" cm="1">
+      <c r="S233" s="25" cm="1">
         <f t="array" ref="S233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>11</v>
       </c>
@@ -9288,63 +9427,63 @@
         <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E234" s="27" cm="1">
+      <c r="E234" s="25" cm="1">
         <f t="array" ref="E234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>12</v>
       </c>
-      <c r="F234" s="27" cm="1">
+      <c r="F234" s="25" cm="1">
         <f t="array" ref="F234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.7</v>
       </c>
-      <c r="G234" s="27" cm="1">
+      <c r="G234" s="25" cm="1">
         <f t="array" ref="G234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H234" s="27" cm="1">
+      <c r="H234" s="25" cm="1">
         <f t="array" ref="H234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.13</v>
       </c>
-      <c r="I234" s="27" cm="1">
+      <c r="I234" s="25" cm="1">
         <f t="array" ref="I234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1E-3</v>
       </c>
-      <c r="J234" s="27" cm="1">
+      <c r="J234" s="25" cm="1">
         <f t="array" ref="J234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K234" s="27" cm="1">
+      <c r="K234" s="25" cm="1">
         <f t="array" ref="K234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L234" s="27" cm="1">
+      <c r="L234" s="25" cm="1">
         <f t="array" ref="L234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M234" s="27" cm="1">
+      <c r="M234" s="25" cm="1">
         <f t="array" ref="M234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N234" s="27" cm="1">
+      <c r="N234" s="25" cm="1">
         <f t="array" ref="N234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O234" s="27" cm="1">
+      <c r="O234" s="25" cm="1">
         <f t="array" ref="O234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P234" s="27" cm="1">
+      <c r="P234" s="25" cm="1">
         <f t="array" ref="P234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q234" s="27" cm="1">
+      <c r="Q234" s="25" cm="1">
         <f t="array" ref="Q234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R234" s="27" cm="1">
+      <c r="R234" s="25" cm="1">
         <f t="array" ref="R234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S234" s="27" cm="1">
+      <c r="S234" s="25" cm="1">
         <f t="array" ref="S234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>12</v>
       </c>
@@ -9354,63 +9493,63 @@
         <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E235" s="27" cm="1">
+      <c r="E235" s="25" cm="1">
         <f t="array" ref="E235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>13</v>
       </c>
-      <c r="F235" s="27" cm="1">
+      <c r="F235" s="25" cm="1">
         <f t="array" ref="F235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.71</v>
       </c>
-      <c r="G235" s="27" cm="1">
+      <c r="G235" s="25" cm="1">
         <f t="array" ref="G235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H235" s="27" cm="1">
+      <c r="H235" s="25" cm="1">
         <f t="array" ref="H235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="I235" s="27" cm="1">
+      <c r="I235" s="25" cm="1">
         <f t="array" ref="I235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1E-3</v>
       </c>
-      <c r="J235" s="27" cm="1">
+      <c r="J235" s="25" cm="1">
         <f t="array" ref="J235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K235" s="27" cm="1">
+      <c r="K235" s="25" cm="1">
         <f t="array" ref="K235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L235" s="27" cm="1">
+      <c r="L235" s="25" cm="1">
         <f t="array" ref="L235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M235" s="27" cm="1">
+      <c r="M235" s="25" cm="1">
         <f t="array" ref="M235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N235" s="27" cm="1">
+      <c r="N235" s="25" cm="1">
         <f t="array" ref="N235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O235" s="27" cm="1">
+      <c r="O235" s="25" cm="1">
         <f t="array" ref="O235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P235" s="27" cm="1">
+      <c r="P235" s="25" cm="1">
         <f t="array" ref="P235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q235" s="27" cm="1">
+      <c r="Q235" s="25" cm="1">
         <f t="array" ref="Q235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R235" s="27" cm="1">
+      <c r="R235" s="25" cm="1">
         <f t="array" ref="R235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S235" s="27" cm="1">
+      <c r="S235" s="25" cm="1">
         <f t="array" ref="S235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>13</v>
       </c>
@@ -9420,63 +9559,63 @@
         <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E236" s="27" cm="1">
+      <c r="E236" s="25" cm="1">
         <f t="array" ref="E236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>14</v>
       </c>
-      <c r="F236" s="27" cm="1">
+      <c r="F236" s="25" cm="1">
         <f t="array" ref="F236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.73</v>
       </c>
-      <c r="G236" s="27" cm="1">
+      <c r="G236" s="25" cm="1">
         <f t="array" ref="G236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H236" s="27" cm="1">
+      <c r="H236" s="25" cm="1">
         <f t="array" ref="H236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.15</v>
       </c>
-      <c r="I236" s="27" cm="1">
+      <c r="I236" s="25" cm="1">
         <f t="array" ref="I236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1E-3</v>
       </c>
-      <c r="J236" s="27" cm="1">
+      <c r="J236" s="25" cm="1">
         <f t="array" ref="J236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K236" s="27" cm="1">
+      <c r="K236" s="25" cm="1">
         <f t="array" ref="K236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L236" s="27" cm="1">
+      <c r="L236" s="25" cm="1">
         <f t="array" ref="L236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M236" s="27" cm="1">
+      <c r="M236" s="25" cm="1">
         <f t="array" ref="M236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N236" s="27" cm="1">
+      <c r="N236" s="25" cm="1">
         <f t="array" ref="N236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O236" s="27" cm="1">
+      <c r="O236" s="25" cm="1">
         <f t="array" ref="O236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P236" s="27" cm="1">
+      <c r="P236" s="25" cm="1">
         <f t="array" ref="P236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q236" s="27" cm="1">
+      <c r="Q236" s="25" cm="1">
         <f t="array" ref="Q236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R236" s="27" cm="1">
+      <c r="R236" s="25" cm="1">
         <f t="array" ref="R236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S236" s="27" cm="1">
+      <c r="S236" s="25" cm="1">
         <f t="array" ref="S236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>14</v>
       </c>
@@ -9486,63 +9625,63 @@
         <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E237" s="27" cm="1">
+      <c r="E237" s="25" cm="1">
         <f t="array" ref="E237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>15</v>
       </c>
-      <c r="F237" s="27" cm="1">
+      <c r="F237" s="25" cm="1">
         <f t="array" ref="F237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.74</v>
       </c>
-      <c r="G237" s="27" cm="1">
+      <c r="G237" s="25" cm="1">
         <f t="array" ref="G237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H237" s="27" cm="1">
+      <c r="H237" s="25" cm="1">
         <f t="array" ref="H237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.17</v>
       </c>
-      <c r="I237" s="27" cm="1">
+      <c r="I237" s="25" cm="1">
         <f t="array" ref="I237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J237" s="27" cm="1">
+      <c r="J237" s="25" cm="1">
         <f t="array" ref="J237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K237" s="27" cm="1">
+      <c r="K237" s="25" cm="1">
         <f t="array" ref="K237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L237" s="27" cm="1">
+      <c r="L237" s="25" cm="1">
         <f t="array" ref="L237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M237" s="27" cm="1">
+      <c r="M237" s="25" cm="1">
         <f t="array" ref="M237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N237" s="27" cm="1">
+      <c r="N237" s="25" cm="1">
         <f t="array" ref="N237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O237" s="27" cm="1">
+      <c r="O237" s="25" cm="1">
         <f t="array" ref="O237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P237" s="27" cm="1">
+      <c r="P237" s="25" cm="1">
         <f t="array" ref="P237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q237" s="27" cm="1">
+      <c r="Q237" s="25" cm="1">
         <f t="array" ref="Q237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R237" s="27" cm="1">
+      <c r="R237" s="25" cm="1">
         <f t="array" ref="R237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S237" s="27" cm="1">
+      <c r="S237" s="25" cm="1">
         <f t="array" ref="S237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>15</v>
       </c>
@@ -9552,63 +9691,63 @@
         <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E238" s="27" cm="1">
+      <c r="E238" s="25" cm="1">
         <f t="array" ref="E238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>16</v>
       </c>
-      <c r="F238" s="27" cm="1">
+      <c r="F238" s="25" cm="1">
         <f t="array" ref="F238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.75</v>
       </c>
-      <c r="G238" s="27" cm="1">
+      <c r="G238" s="25" cm="1">
         <f t="array" ref="G238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H238" s="27" cm="1">
+      <c r="H238" s="25" cm="1">
         <f t="array" ref="H238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.18</v>
       </c>
-      <c r="I238" s="27" cm="1">
+      <c r="I238" s="25" cm="1">
         <f t="array" ref="I238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J238" s="27" cm="1">
+      <c r="J238" s="25" cm="1">
         <f t="array" ref="J238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K238" s="27" cm="1">
+      <c r="K238" s="25" cm="1">
         <f t="array" ref="K238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L238" s="27" cm="1">
+      <c r="L238" s="25" cm="1">
         <f t="array" ref="L238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M238" s="27" cm="1">
+      <c r="M238" s="25" cm="1">
         <f t="array" ref="M238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N238" s="27" cm="1">
+      <c r="N238" s="25" cm="1">
         <f t="array" ref="N238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O238" s="27" cm="1">
+      <c r="O238" s="25" cm="1">
         <f t="array" ref="O238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P238" s="27" cm="1">
+      <c r="P238" s="25" cm="1">
         <f t="array" ref="P238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q238" s="27" cm="1">
+      <c r="Q238" s="25" cm="1">
         <f t="array" ref="Q238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R238" s="27" cm="1">
+      <c r="R238" s="25" cm="1">
         <f t="array" ref="R238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S238" s="27" cm="1">
+      <c r="S238" s="25" cm="1">
         <f t="array" ref="S238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>16</v>
       </c>
@@ -9618,63 +9757,63 @@
         <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E239" s="27" cm="1">
+      <c r="E239" s="25" cm="1">
         <f t="array" ref="E239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>17</v>
       </c>
-      <c r="F239" s="27" cm="1">
+      <c r="F239" s="25" cm="1">
         <f t="array" ref="F239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.76</v>
       </c>
-      <c r="G239" s="27" cm="1">
+      <c r="G239" s="25" cm="1">
         <f t="array" ref="G239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H239" s="27" cm="1">
+      <c r="H239" s="25" cm="1">
         <f t="array" ref="H239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.2</v>
       </c>
-      <c r="I239" s="27" cm="1">
+      <c r="I239" s="25" cm="1">
         <f t="array" ref="I239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J239" s="27" cm="1">
+      <c r="J239" s="25" cm="1">
         <f t="array" ref="J239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K239" s="27" cm="1">
+      <c r="K239" s="25" cm="1">
         <f t="array" ref="K239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L239" s="27" cm="1">
+      <c r="L239" s="25" cm="1">
         <f t="array" ref="L239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M239" s="27" cm="1">
+      <c r="M239" s="25" cm="1">
         <f t="array" ref="M239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N239" s="27" cm="1">
+      <c r="N239" s="25" cm="1">
         <f t="array" ref="N239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O239" s="27" cm="1">
+      <c r="O239" s="25" cm="1">
         <f t="array" ref="O239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P239" s="27" cm="1">
+      <c r="P239" s="25" cm="1">
         <f t="array" ref="P239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q239" s="27" cm="1">
+      <c r="Q239" s="25" cm="1">
         <f t="array" ref="Q239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R239" s="27" cm="1">
+      <c r="R239" s="25" cm="1">
         <f t="array" ref="R239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S239" s="27" cm="1">
+      <c r="S239" s="25" cm="1">
         <f t="array" ref="S239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>17</v>
       </c>
@@ -9684,63 +9823,63 @@
         <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E240" s="27" cm="1">
+      <c r="E240" s="25" cm="1">
         <f t="array" ref="E240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>18</v>
       </c>
-      <c r="F240" s="27" cm="1">
+      <c r="F240" s="25" cm="1">
         <f t="array" ref="F240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.77</v>
       </c>
-      <c r="G240" s="27" cm="1">
+      <c r="G240" s="25" cm="1">
         <f t="array" ref="G240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H240" s="27" cm="1">
+      <c r="H240" s="25" cm="1">
         <f t="array" ref="H240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.22</v>
       </c>
-      <c r="I240" s="27" cm="1">
+      <c r="I240" s="25" cm="1">
         <f t="array" ref="I240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J240" s="27" cm="1">
+      <c r="J240" s="25" cm="1">
         <f t="array" ref="J240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K240" s="27" cm="1">
+      <c r="K240" s="25" cm="1">
         <f t="array" ref="K240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L240" s="27" cm="1">
+      <c r="L240" s="25" cm="1">
         <f t="array" ref="L240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M240" s="27" cm="1">
+      <c r="M240" s="25" cm="1">
         <f t="array" ref="M240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N240" s="27" cm="1">
+      <c r="N240" s="25" cm="1">
         <f t="array" ref="N240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O240" s="27" cm="1">
+      <c r="O240" s="25" cm="1">
         <f t="array" ref="O240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P240" s="27" cm="1">
+      <c r="P240" s="25" cm="1">
         <f t="array" ref="P240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q240" s="27" cm="1">
+      <c r="Q240" s="25" cm="1">
         <f t="array" ref="Q240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R240" s="27" cm="1">
+      <c r="R240" s="25" cm="1">
         <f t="array" ref="R240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S240" s="27" cm="1">
+      <c r="S240" s="25" cm="1">
         <f t="array" ref="S240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>18</v>
       </c>
@@ -9750,63 +9889,63 @@
         <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E241" s="27" cm="1">
+      <c r="E241" s="25" cm="1">
         <f t="array" ref="E241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>19</v>
       </c>
-      <c r="F241" s="27" cm="1">
+      <c r="F241" s="25" cm="1">
         <f t="array" ref="F241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.77</v>
       </c>
-      <c r="G241" s="27" cm="1">
+      <c r="G241" s="25" cm="1">
         <f t="array" ref="G241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H241" s="27" cm="1">
+      <c r="H241" s="25" cm="1">
         <f t="array" ref="H241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.24</v>
       </c>
-      <c r="I241" s="27" cm="1">
+      <c r="I241" s="25" cm="1">
         <f t="array" ref="I241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J241" s="27" cm="1">
+      <c r="J241" s="25" cm="1">
         <f t="array" ref="J241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K241" s="27" cm="1">
+      <c r="K241" s="25" cm="1">
         <f t="array" ref="K241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L241" s="27" cm="1">
+      <c r="L241" s="25" cm="1">
         <f t="array" ref="L241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M241" s="27" cm="1">
+      <c r="M241" s="25" cm="1">
         <f t="array" ref="M241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N241" s="27" cm="1">
+      <c r="N241" s="25" cm="1">
         <f t="array" ref="N241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O241" s="27" cm="1">
+      <c r="O241" s="25" cm="1">
         <f t="array" ref="O241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P241" s="27" cm="1">
+      <c r="P241" s="25" cm="1">
         <f t="array" ref="P241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q241" s="27" cm="1">
+      <c r="Q241" s="25" cm="1">
         <f t="array" ref="Q241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R241" s="27" cm="1">
+      <c r="R241" s="25" cm="1">
         <f t="array" ref="R241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S241" s="27" cm="1">
+      <c r="S241" s="25" cm="1">
         <f t="array" ref="S241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>19</v>
       </c>
@@ -9816,63 +9955,63 @@
         <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E242" s="27" cm="1">
+      <c r="E242" s="25" cm="1">
         <f t="array" ref="E242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>20</v>
       </c>
-      <c r="F242" s="27" cm="1">
+      <c r="F242" s="25" cm="1">
         <f t="array" ref="F242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.78</v>
       </c>
-      <c r="G242" s="27" cm="1">
+      <c r="G242" s="25" cm="1">
         <f t="array" ref="G242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H242" s="27" cm="1">
+      <c r="H242" s="25" cm="1">
         <f t="array" ref="H242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.26</v>
       </c>
-      <c r="I242" s="27" cm="1">
+      <c r="I242" s="25" cm="1">
         <f t="array" ref="I242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J242" s="27" cm="1">
+      <c r="J242" s="25" cm="1">
         <f t="array" ref="J242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K242" s="27" cm="1">
+      <c r="K242" s="25" cm="1">
         <f t="array" ref="K242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L242" s="27" cm="1">
+      <c r="L242" s="25" cm="1">
         <f t="array" ref="L242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M242" s="27" cm="1">
+      <c r="M242" s="25" cm="1">
         <f t="array" ref="M242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N242" s="27" cm="1">
+      <c r="N242" s="25" cm="1">
         <f t="array" ref="N242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O242" s="27" cm="1">
+      <c r="O242" s="25" cm="1">
         <f t="array" ref="O242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P242" s="27" cm="1">
+      <c r="P242" s="25" cm="1">
         <f t="array" ref="P242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q242" s="27" cm="1">
+      <c r="Q242" s="25" cm="1">
         <f t="array" ref="Q242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R242" s="27" cm="1">
+      <c r="R242" s="25" cm="1">
         <f t="array" ref="R242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S242" s="27" cm="1">
+      <c r="S242" s="25" cm="1">
         <f t="array" ref="S242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>20</v>
       </c>
@@ -9882,63 +10021,63 @@
         <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E243" s="27" cm="1">
+      <c r="E243" s="25" cm="1">
         <f t="array" ref="E243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>21</v>
       </c>
-      <c r="F243" s="27" cm="1">
+      <c r="F243" s="25" cm="1">
         <f t="array" ref="F243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.78</v>
       </c>
-      <c r="G243" s="27" cm="1">
+      <c r="G243" s="25" cm="1">
         <f t="array" ref="G243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H243" s="27" cm="1">
+      <c r="H243" s="25" cm="1">
         <f t="array" ref="H243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="I243" s="27" cm="1">
+      <c r="I243" s="25" cm="1">
         <f t="array" ref="I243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J243" s="27" cm="1">
+      <c r="J243" s="25" cm="1">
         <f t="array" ref="J243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K243" s="27" cm="1">
+      <c r="K243" s="25" cm="1">
         <f t="array" ref="K243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L243" s="27" cm="1">
+      <c r="L243" s="25" cm="1">
         <f t="array" ref="L243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M243" s="27" cm="1">
+      <c r="M243" s="25" cm="1">
         <f t="array" ref="M243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N243" s="27" cm="1">
+      <c r="N243" s="25" cm="1">
         <f t="array" ref="N243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O243" s="27" cm="1">
+      <c r="O243" s="25" cm="1">
         <f t="array" ref="O243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P243" s="27" cm="1">
+      <c r="P243" s="25" cm="1">
         <f t="array" ref="P243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q243" s="27" cm="1">
+      <c r="Q243" s="25" cm="1">
         <f t="array" ref="Q243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R243" s="27" cm="1">
+      <c r="R243" s="25" cm="1">
         <f t="array" ref="R243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S243" s="27" cm="1">
+      <c r="S243" s="25" cm="1">
         <f t="array" ref="S243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>21</v>
       </c>
@@ -9948,63 +10087,63 @@
         <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E244" s="27" cm="1">
+      <c r="E244" s="25" cm="1">
         <f t="array" ref="E244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>22</v>
       </c>
-      <c r="F244" s="27" cm="1">
+      <c r="F244" s="25" cm="1">
         <f t="array" ref="F244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.78</v>
       </c>
-      <c r="G244" s="27" cm="1">
+      <c r="G244" s="25" cm="1">
         <f t="array" ref="G244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H244" s="27" cm="1">
+      <c r="H244" s="25" cm="1">
         <f t="array" ref="H244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.31</v>
       </c>
-      <c r="I244" s="27" cm="1">
+      <c r="I244" s="25" cm="1">
         <f t="array" ref="I244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J244" s="27" cm="1">
+      <c r="J244" s="25" cm="1">
         <f t="array" ref="J244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K244" s="27" cm="1">
+      <c r="K244" s="25" cm="1">
         <f t="array" ref="K244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L244" s="27" cm="1">
+      <c r="L244" s="25" cm="1">
         <f t="array" ref="L244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M244" s="27" cm="1">
+      <c r="M244" s="25" cm="1">
         <f t="array" ref="M244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N244" s="27" cm="1">
+      <c r="N244" s="25" cm="1">
         <f t="array" ref="N244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O244" s="27" cm="1">
+      <c r="O244" s="25" cm="1">
         <f t="array" ref="O244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P244" s="27" cm="1">
+      <c r="P244" s="25" cm="1">
         <f t="array" ref="P244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q244" s="27" cm="1">
+      <c r="Q244" s="25" cm="1">
         <f t="array" ref="Q244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R244" s="27" cm="1">
+      <c r="R244" s="25" cm="1">
         <f t="array" ref="R244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S244" s="27" cm="1">
+      <c r="S244" s="25" cm="1">
         <f t="array" ref="S244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>22</v>
       </c>
@@ -10014,63 +10153,63 @@
         <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E245" s="27" cm="1">
+      <c r="E245" s="25" cm="1">
         <f t="array" ref="E245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>23</v>
       </c>
-      <c r="F245" s="27" cm="1">
+      <c r="F245" s="25" cm="1">
         <f t="array" ref="F245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.79</v>
       </c>
-      <c r="G245" s="27" cm="1">
+      <c r="G245" s="25" cm="1">
         <f t="array" ref="G245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H245" s="27" cm="1">
+      <c r="H245" s="25" cm="1">
         <f t="array" ref="H245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.34</v>
       </c>
-      <c r="I245" s="27" cm="1">
+      <c r="I245" s="25" cm="1">
         <f t="array" ref="I245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J245" s="27" cm="1">
+      <c r="J245" s="25" cm="1">
         <f t="array" ref="J245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K245" s="27" cm="1">
+      <c r="K245" s="25" cm="1">
         <f t="array" ref="K245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L245" s="27" cm="1">
+      <c r="L245" s="25" cm="1">
         <f t="array" ref="L245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M245" s="27" cm="1">
+      <c r="M245" s="25" cm="1">
         <f t="array" ref="M245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N245" s="27" cm="1">
+      <c r="N245" s="25" cm="1">
         <f t="array" ref="N245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O245" s="27" cm="1">
+      <c r="O245" s="25" cm="1">
         <f t="array" ref="O245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P245" s="27" cm="1">
+      <c r="P245" s="25" cm="1">
         <f t="array" ref="P245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q245" s="27" cm="1">
+      <c r="Q245" s="25" cm="1">
         <f t="array" ref="Q245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R245" s="27" cm="1">
+      <c r="R245" s="25" cm="1">
         <f t="array" ref="R245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S245" s="27" cm="1">
+      <c r="S245" s="25" cm="1">
         <f t="array" ref="S245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>23</v>
       </c>
@@ -10080,63 +10219,63 @@
         <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E246" s="27" cm="1">
+      <c r="E246" s="25" cm="1">
         <f t="array" ref="E246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>24</v>
       </c>
-      <c r="F246" s="27" cm="1">
+      <c r="F246" s="25" cm="1">
         <f t="array" ref="F246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.79</v>
       </c>
-      <c r="G246" s="27" cm="1">
+      <c r="G246" s="25" cm="1">
         <f t="array" ref="G246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H246" s="27" cm="1">
+      <c r="H246" s="25" cm="1">
         <f t="array" ref="H246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.37</v>
       </c>
-      <c r="I246" s="27" cm="1">
+      <c r="I246" s="25" cm="1">
         <f t="array" ref="I246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J246" s="27" cm="1">
+      <c r="J246" s="25" cm="1">
         <f t="array" ref="J246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K246" s="27" cm="1">
+      <c r="K246" s="25" cm="1">
         <f t="array" ref="K246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L246" s="27" cm="1">
+      <c r="L246" s="25" cm="1">
         <f t="array" ref="L246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M246" s="27" cm="1">
+      <c r="M246" s="25" cm="1">
         <f t="array" ref="M246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N246" s="27" cm="1">
+      <c r="N246" s="25" cm="1">
         <f t="array" ref="N246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O246" s="27" cm="1">
+      <c r="O246" s="25" cm="1">
         <f t="array" ref="O246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P246" s="27" cm="1">
+      <c r="P246" s="25" cm="1">
         <f t="array" ref="P246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q246" s="27" cm="1">
+      <c r="Q246" s="25" cm="1">
         <f t="array" ref="Q246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R246" s="27" cm="1">
+      <c r="R246" s="25" cm="1">
         <f t="array" ref="R246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S246" s="27" cm="1">
+      <c r="S246" s="25" cm="1">
         <f t="array" ref="S246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>24</v>
       </c>
@@ -10146,63 +10285,63 @@
         <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E247" s="27" cm="1">
+      <c r="E247" s="25" cm="1">
         <f t="array" ref="E247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>25</v>
       </c>
-      <c r="F247" s="27" cm="1">
+      <c r="F247" s="25" cm="1">
         <f t="array" ref="F247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.79</v>
       </c>
-      <c r="G247" s="27" cm="1">
+      <c r="G247" s="25" cm="1">
         <f t="array" ref="G247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H247" s="27" cm="1">
+      <c r="H247" s="25" cm="1">
         <f t="array" ref="H247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.41</v>
       </c>
-      <c r="I247" s="27" cm="1">
+      <c r="I247" s="25" cm="1">
         <f t="array" ref="I247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J247" s="27" cm="1">
+      <c r="J247" s="25" cm="1">
         <f t="array" ref="J247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K247" s="27" cm="1">
+      <c r="K247" s="25" cm="1">
         <f t="array" ref="K247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L247" s="27" cm="1">
+      <c r="L247" s="25" cm="1">
         <f t="array" ref="L247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M247" s="27" cm="1">
+      <c r="M247" s="25" cm="1">
         <f t="array" ref="M247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N247" s="27" cm="1">
+      <c r="N247" s="25" cm="1">
         <f t="array" ref="N247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O247" s="27" cm="1">
+      <c r="O247" s="25" cm="1">
         <f t="array" ref="O247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P247" s="27" cm="1">
+      <c r="P247" s="25" cm="1">
         <f t="array" ref="P247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q247" s="27" cm="1">
+      <c r="Q247" s="25" cm="1">
         <f t="array" ref="Q247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R247" s="27" cm="1">
+      <c r="R247" s="25" cm="1">
         <f t="array" ref="R247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S247" s="27" cm="1">
+      <c r="S247" s="25" cm="1">
         <f t="array" ref="S247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>25</v>
       </c>
@@ -10212,63 +10351,63 @@
         <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
       </c>
-      <c r="E248" s="27" cm="1">
+      <c r="E248" s="25" cm="1">
         <f t="array" ref="E248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>26</v>
       </c>
-      <c r="F248" s="27" cm="1">
+      <c r="F248" s="25" cm="1">
         <f t="array" ref="F248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.79</v>
       </c>
-      <c r="G248" s="27" cm="1">
+      <c r="G248" s="25" cm="1">
         <f t="array" ref="G248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H248" s="27" cm="1">
+      <c r="H248" s="25" cm="1">
         <f t="array" ref="H248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.44</v>
       </c>
-      <c r="I248" s="27" cm="1">
+      <c r="I248" s="25" cm="1">
         <f t="array" ref="I248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="J248" s="27" cm="1">
+      <c r="J248" s="25" cm="1">
         <f t="array" ref="J248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="K248" s="27" cm="1">
+      <c r="K248" s="25" cm="1">
         <f t="array" ref="K248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L248" s="27" cm="1">
+      <c r="L248" s="25" cm="1">
         <f t="array" ref="L248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M248" s="27" cm="1">
+      <c r="M248" s="25" cm="1">
         <f t="array" ref="M248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N248" s="27" cm="1">
+      <c r="N248" s="25" cm="1">
         <f t="array" ref="N248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O248" s="27" cm="1">
+      <c r="O248" s="25" cm="1">
         <f t="array" ref="O248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P248" s="27" cm="1">
+      <c r="P248" s="25" cm="1">
         <f t="array" ref="P248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q248" s="27" cm="1">
+      <c r="Q248" s="25" cm="1">
         <f t="array" ref="Q248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R248" s="27" cm="1">
+      <c r="R248" s="25" cm="1">
         <f t="array" ref="R248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S248" s="27" cm="1">
+      <c r="S248" s="25" cm="1">
         <f t="array" ref="S248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>26</v>
       </c>
@@ -10278,63 +10417,63 @@
         <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
       </c>
-      <c r="E249" s="27" cm="1">
+      <c r="E249" s="25" cm="1">
         <f t="array" ref="E249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>27</v>
       </c>
-      <c r="F249" s="27" cm="1">
+      <c r="F249" s="25" cm="1">
         <f t="array" ref="F249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.8</v>
       </c>
-      <c r="G249" s="27" cm="1">
+      <c r="G249" s="25" cm="1">
         <f t="array" ref="G249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H249" s="27" cm="1">
+      <c r="H249" s="25" cm="1">
         <f t="array" ref="H249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.48</v>
       </c>
-      <c r="I249" s="27" cm="1">
+      <c r="I249" s="25" cm="1">
         <f t="array" ref="I249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="J249" s="27" cm="1">
+      <c r="J249" s="25" cm="1">
         <f t="array" ref="J249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="K249" s="27" cm="1">
+      <c r="K249" s="25" cm="1">
         <f t="array" ref="K249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L249" s="27" cm="1">
+      <c r="L249" s="25" cm="1">
         <f t="array" ref="L249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M249" s="27" cm="1">
+      <c r="M249" s="25" cm="1">
         <f t="array" ref="M249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N249" s="27" cm="1">
+      <c r="N249" s="25" cm="1">
         <f t="array" ref="N249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O249" s="27" cm="1">
+      <c r="O249" s="25" cm="1">
         <f t="array" ref="O249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P249" s="27" cm="1">
+      <c r="P249" s="25" cm="1">
         <f t="array" ref="P249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q249" s="27" cm="1">
+      <c r="Q249" s="25" cm="1">
         <f t="array" ref="Q249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R249" s="27" cm="1">
+      <c r="R249" s="25" cm="1">
         <f t="array" ref="R249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S249" s="27" cm="1">
+      <c r="S249" s="25" cm="1">
         <f t="array" ref="S249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>27</v>
       </c>
@@ -10344,63 +10483,63 @@
         <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
       </c>
-      <c r="E250" s="27" t="str" cm="1">
+      <c r="E250" s="25" t="str" cm="1">
         <f t="array" ref="E250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>≥28</v>
       </c>
-      <c r="F250" s="27" cm="1">
+      <c r="F250" s="25" cm="1">
         <f t="array" ref="F250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.8</v>
       </c>
-      <c r="G250" s="27" cm="1">
+      <c r="G250" s="25" cm="1">
         <f t="array" ref="G250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H250" s="27" cm="1">
+      <c r="H250" s="25" cm="1">
         <f t="array" ref="H250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.5</v>
       </c>
-      <c r="I250" s="27" cm="1">
+      <c r="I250" s="25" cm="1">
         <f t="array" ref="I250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="J250" s="27" cm="1">
+      <c r="J250" s="25" cm="1">
         <f t="array" ref="J250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="K250" s="27" cm="1">
+      <c r="K250" s="25" cm="1">
         <f t="array" ref="K250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L250" s="27" cm="1">
+      <c r="L250" s="25" cm="1">
         <f t="array" ref="L250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M250" s="27" cm="1">
+      <c r="M250" s="25" cm="1">
         <f t="array" ref="M250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N250" s="27" cm="1">
+      <c r="N250" s="25" cm="1">
         <f t="array" ref="N250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O250" s="27" cm="1">
+      <c r="O250" s="25" cm="1">
         <f t="array" ref="O250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P250" s="27" cm="1">
+      <c r="P250" s="25" cm="1">
         <f t="array" ref="P250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q250" s="27" cm="1">
+      <c r="Q250" s="25" cm="1">
         <f t="array" ref="Q250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R250" s="27" cm="1">
+      <c r="R250" s="25" cm="1">
         <f t="array" ref="R250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S250" s="27" cm="1">
+      <c r="S250" s="25" cm="1">
         <f t="array" ref="S250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>28</v>
       </c>
@@ -10424,25 +10563,25 @@
       </c>
     </row>
     <row r="256" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D256" s="29" t="str" cm="1">
+      <c r="D256" s="27" t="str" cm="1">
         <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
     <row r="257" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D257" s="27" t="s">
+      <c r="D257" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="E257" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="E257" s="27" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="258" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D258" s="27" t="str" cm="1">
+      <c r="D258" s="25" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
-      <c r="E258" s="27" cm="1">
+      <c r="E258" s="25" cm="1">
         <f t="array" ref="E258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>6.0000000000000001E-3</v>
       </c>
@@ -10452,7 +10591,7 @@
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
-      <c r="E259" s="27" cm="1">
+      <c r="E259" s="25" cm="1">
         <f t="array" ref="E259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
@@ -10483,15 +10622,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -10686,7 +10816,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -10697,19 +10827,20 @@
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMgAuADEAOgAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAyAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBRAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgACgAawBnACAAQwBPADIAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsAFwAbgAgACAAIAAgAFEAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMgAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFEAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBUAGkAdABsAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFUAbgBpAHQAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AUwBvAHUAcgBjAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10728,7 +10859,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -10739,10 +10870,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Excel/12_SupplementaryCO2_WIP_v02.xlsx
+++ b/Excel/12_SupplementaryCO2_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F68347-82B0-4783-BFE1-E6372EEC1A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987D1495-E8FA-43C4-AF66-ED79033C198A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" firstSheet="5" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15345" firstSheet="5" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -6074,8 +6074,8 @@
       <c r="D7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="10" t="str" cm="1">
-        <f t="array" aca="1" ref="E7" ca="1">Common_InputFunctions.Utility_DisplayFunctionName(E15)</f>
+      <c r="E7" s="10" t="str">
+        <f ca="1">Common_InputFunctions.Utility_DisplayFunctionName(VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2_Result_Method1)</f>
         <v>=SupplementaryCO2_Equations.VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2</v>
       </c>
       <c r="O7" s="42"/>
@@ -10622,6 +10622,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMgAuADEAOgAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAyAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBRAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgACgAawBnACAAQwBPADIAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsAFwAbgAgACAAIAAgAFEAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMgAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFEAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoA